--- a/outputs/gold-review-30/gold-review-30.xlsx
+++ b/outputs/gold-review-30/gold-review-30.xlsx
@@ -2,10 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R27303b73751b4310"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Queue" sheetId="2" r:id="Ra1a4ca4f05ff42ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="3" r:id="R55672693004d4804"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="4" r:id="R9b2f95abd5ca49fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Form" sheetId="1" r:id="R115200cfa1d44957"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="3" r:id="R37b504269bf541ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="4" r:id="Rc3561c99613f41fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,7 +21,7 @@
     <x:numFmt numFmtId="202" formatCode="0"/>
     <x:numFmt numFmtId="203" formatCode="0.00000000"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="18">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -101,8 +100,31 @@
       <x:color rgb="FF7A5300"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF355268"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF233746"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="51">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -144,8 +166,218 @@
         <x:fgColor rgb="FFFFFDF5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17324D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F75B5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F6F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17324D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F75B5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F6F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17324D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F75B5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F6F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17324D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F75B5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F6F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17324D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F75B5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F6F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17324D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F75B5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F6F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17324D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F75B5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F6F8"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="12">
+  <x:borders count="18">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -268,11 +500,59 @@
         <x:color rgb="FFE3B341"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF2F75B5"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF2F75B5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF2F75B5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FF2F75B5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF2F75B5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF2F75B5"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF2F75B5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF2F75B5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2EA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2EA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2EA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2EA"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="100">
+  <x:cellXfs count="611">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -503,18 +783,1187 @@
     <x:xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="14" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="14" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="14" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="14" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="14" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="19" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="19" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="19" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="19" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="20" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="24" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="24" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="24" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="24" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="24" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="24" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="24" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="24" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="24" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="25" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="25" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="25" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="25" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="25" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="25" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="25" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="25" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="25" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="24" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="24" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="24" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="26" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="26" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="26" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="25" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="25" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="25" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="26" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="26" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="26" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="30" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="30" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="30" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="30" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="30" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="30" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="30" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="30" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="30" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="31" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="31" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="31" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="31" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="31" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="31" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="31" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="31" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="31" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="32" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="32" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="32" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="32" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="32" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="32" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="32" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="32" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="32" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="30" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="30" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="30" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="31" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="31" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="31" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="32" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="32" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="32" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="35" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="36" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="36" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="36" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="36" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="36" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="36" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="36" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="36" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="36" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="37" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="37" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="37" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="37" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="37" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="37" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="37" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="37" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="37" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="38" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="38" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="38" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="38" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="38" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="38" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="38" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="38" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="38" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="36" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="36" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="36" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="38" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="38" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="38" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="37" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="37" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="37" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="38" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="38" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="38" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="41" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="41" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="41" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="41" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="41" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="41" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="41" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="41" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="41" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="42" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="42" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="42" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="42" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="42" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="42" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="42" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="42" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="42" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="43" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="43" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="43" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="43" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="43" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="43" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="43" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="43" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="43" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="44" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="44" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="44" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="44" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="44" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="44" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="44" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="44" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="44" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="42" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="42" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="42" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="44" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="44" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="44" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="43" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="43" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="43" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="44" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="44" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="44" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="47" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="47" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="47" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="47" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="47" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="47" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="47" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="47" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="47" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="47" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="47" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="47" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="48" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="48" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="48" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="48" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="48" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="48" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="48" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="48" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="48" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="48" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="48" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="49" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="49" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="49" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="49" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="49" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="49" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="49" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="49" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="49" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="49" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="49" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="50" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="50" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="50" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="50" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="50" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="50" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="50" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="50" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="50" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="48" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="48" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="48" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="50" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="50" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="50" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="49" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="49" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="49" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="50" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="50" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="50" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="31">
     <x:dxf>
       <x:font>
         <x:b/>
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -525,7 +1974,7 @@
         <x:color rgb="FF1D4ED8"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF2FB"/>
         </x:patternFill>
       </x:fill>
@@ -536,8 +1985,288 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFEE2E2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F6000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF375623"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF1F4E78"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDDEBF7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF843C0C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F6000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF375623"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF1F4E78"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDDEBF7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF843C0C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F6000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF375623"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF1F4E78"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDDEBF7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF843C0C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F6000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF375623"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF1F4E78"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDDEBF7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF843C0C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F6000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF375623"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF1F4E78"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDDEBF7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF843C0C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F6000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF375623"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF1F4E78"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDDEBF7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF843C0C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F6000"/>
+      </x:font>
+      <x:fill>
         <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE2E2"/>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF375623"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF1F4E78"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDEBF7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF843C0C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -546,34 +2275,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReviewQueueTable" displayName="ReviewQueueTable" ref="A5:S35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="19">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ReviewFormTable" displayName="ReviewFormTable" ref="A7:I37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:I37"/>
+  <x:tableColumns count="9">
     <x:tableColumn id="1" name="question_id"/>
-    <x:tableColumn id="2" name="seed_id"/>
-    <x:tableColumn id="3" name="language"/>
-    <x:tableColumn id="4" name="topic"/>
-    <x:tableColumn id="5" name="difficulty"/>
-    <x:tableColumn id="6" name="Status"/>
-    <x:tableColumn id="7" name="expected_route"/>
-    <x:tableColumn id="8" name="question"/>
-    <x:tableColumn id="9" name="parent context"/>
-    <x:tableColumn id="10" name="expected no result"/>
-    <x:tableColumn id="11" name="proposed source IDs"/>
-    <x:tableColumn id="12" name="proposed chunk IDs"/>
-    <x:tableColumn id="13" name="proposed rationale"/>
-    <x:tableColumn id="14" name="human_relevant_chunk_ids"/>
-    <x:tableColumn id="15" name="reviewer"/>
-    <x:tableColumn id="16" name="reviewed_at"/>
-    <x:tableColumn id="17" name="correction_notes"/>
-    <x:tableColumn id="18" name="production mode"/>
-    <x:tableColumn id="19" name="packet state"/>
+    <x:tableColumn id="2" name="language"/>
+    <x:tableColumn id="3" name="question"/>
+    <x:tableColumn id="4" name="proposed evidence summary"/>
+    <x:tableColumn id="5" name="status"/>
+    <x:tableColumn id="6" name="human_relevant_chunk_ids"/>
+    <x:tableColumn id="7" name="correction_notes"/>
+    <x:tableColumn id="8" name="reviewer"/>
+    <x:tableColumn id="9" name="reviewed_at"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ReviewExportTable" displayName="ReviewExportTable" ref="K7:P37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="K7:P37"/>
+  <x:tableColumns count="6">
+    <x:tableColumn id="1" name="question_id"/>
+    <x:tableColumn id="2" name="status"/>
+    <x:tableColumn id="3" name="human_relevant_chunk_ids"/>
+    <x:tableColumn id="4" name="reviewer"/>
+    <x:tableColumn id="5" name="reviewed_at"/>
+    <x:tableColumn id="6" name="correction_notes"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EvidenceTable" displayName="EvidenceTable" ref="A5:M605" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:M605"/>
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="question_id"/>
     <x:tableColumn id="2" name="mode"/>
@@ -788,1948 +2524,1444 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="27" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="46" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="58" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="3" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="15" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>Napas Jakarta · 30-question review queue</x:v>
-      </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
-      <x:c r="G1" s="4"/>
-      <x:c r="H1" s="4"/>
-    </x:row>
-    <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="8" t="str">
-        <x:v>Machine-suggested evidence packet for a focused human review pass. The queue is not approved until every row is decided.</x:v>
-      </x:c>
-      <x:c r="B2" s="8"/>
-      <x:c r="C2" s="8"/>
-      <x:c r="D2" s="8"/>
-      <x:c r="E2" s="8"/>
-      <x:c r="F2" s="8"/>
-      <x:c r="G2" s="8"/>
-      <x:c r="H2" s="8"/>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="17" t="str">
-        <x:v>PENDING HUMAN REVIEW — proposed source/chunk labels are suggestions only. Review the Evidence sheet, then edit Status and the blank human fields on Review Queue.</x:v>
-      </x:c>
-      <x:c r="B4" s="18"/>
-      <x:c r="C4" s="18"/>
-      <x:c r="D4" s="18"/>
-      <x:c r="E4" s="18"/>
-      <x:c r="F4" s="18"/>
-      <x:c r="G4" s="18"/>
-      <x:c r="H4" s="19"/>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="541" t="str">
+        <x:v>Human evidence review</x:v>
+      </x:c>
+      <x:c r="B1" s="541"/>
+      <x:c r="C1" s="541"/>
+      <x:c r="D1" s="541"/>
+      <x:c r="E1" s="541"/>
+      <x:c r="F1" s="541"/>
+      <x:c r="G1" s="541"/>
+      <x:c r="H1" s="541"/>
+      <x:c r="I1" s="541"/>
+      <x:c r="J1" s="541"/>
+      <x:c r="K1" s="541"/>
+      <x:c r="L1" s="541"/>
+      <x:c r="M1" s="541"/>
+      <x:c r="N1" s="541"/>
+      <x:c r="O1" s="541"/>
+      <x:c r="P1" s="541"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="545" t="str">
+        <x:v>Review each question, check the proposed evidence against Evidence, and complete the yellow cells.</x:v>
+      </x:c>
+      <x:c r="B2" s="545"/>
+      <x:c r="C2" s="545"/>
+      <x:c r="D2" s="545"/>
+      <x:c r="E2" s="545"/>
+      <x:c r="F2" s="545"/>
+      <x:c r="G2" s="545"/>
+      <x:c r="H2" s="545"/>
+      <x:c r="I2" s="545"/>
+      <x:c r="J2" s="545"/>
+      <x:c r="K2" s="545"/>
+      <x:c r="L2" s="545"/>
+      <x:c r="M2" s="545"/>
+      <x:c r="N2" s="545"/>
+      <x:c r="O2" s="545"/>
+      <x:c r="P2" s="545"/>
+    </x:row>
+    <x:row r="4" ht="22" customHeight="1">
+      <x:c r="A4" s="549" t="str">
+        <x:v>How to complete this sheet</x:v>
+      </x:c>
+      <x:c r="B4" s="549"/>
+      <x:c r="C4" s="549"/>
+      <x:c r="D4" s="549"/>
+      <x:c r="E4" s="549"/>
+      <x:c r="F4" s="549"/>
+      <x:c r="G4" s="549"/>
+      <x:c r="H4" s="549"/>
+      <x:c r="I4" s="549"/>
+      <x:c r="K4" s="549" t="str">
+        <x:v>Export-ready fields</x:v>
+      </x:c>
+      <x:c r="L4" s="549"/>
+      <x:c r="M4" s="549"/>
+      <x:c r="N4" s="549"/>
+      <x:c r="O4" s="549"/>
+      <x:c r="P4" s="549"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="552" t="str">
+        <x:v>Approved = proposal is correct. Corrected = change the chunk IDs. Rejected = unsupported or unusable. Use exact chunk IDs from Evidence column E, separated by commas, with no locator suffix such as (p.1).</x:v>
+      </x:c>
+      <x:c r="B5" s="552"/>
+      <x:c r="C5" s="552"/>
+      <x:c r="D5" s="552"/>
+      <x:c r="E5" s="552"/>
+      <x:c r="F5" s="552"/>
+      <x:c r="G5" s="552"/>
+      <x:c r="H5" s="552"/>
+      <x:c r="I5" s="552"/>
+      <x:c r="K5" s="552" t="str">
+        <x:v>This six-column section mirrors the yellow review fields and is ready to export as CSV.</x:v>
+      </x:c>
+      <x:c r="L5" s="552"/>
+      <x:c r="M5" s="552"/>
+      <x:c r="N5" s="552"/>
+      <x:c r="O5" s="552"/>
+      <x:c r="P5" s="552"/>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="28" t="str">
-        <x:v>Progress</x:v>
-      </x:c>
-      <x:c r="B6" s="29" t="str">
-        <x:v>Count</x:v>
-      </x:c>
-      <x:c r="D6" s="28" t="str">
-        <x:v>Language</x:v>
-      </x:c>
-      <x:c r="E6" s="29" t="str">
-        <x:v>Count</x:v>
-      </x:c>
-      <x:c r="G6" s="28" t="str">
-        <x:v>Corpus snapshot</x:v>
-      </x:c>
-      <x:c r="H6" s="29" t="str">
-        <x:v>Value</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="32" t="str">
-        <x:v>Total questions</x:v>
-      </x:c>
-      <x:c r="B7" s="36" t="n">
-        <x:f>COUNTA('Review Queue'!$A$6:$A$35)</x:f>
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D7" s="32" t="str">
+      <x:c r="A6"/>
+      <x:c r="B6"/>
+      <x:c r="D6"/>
+      <x:c r="E6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="563" t="str">
+        <x:v>question_id</x:v>
+      </x:c>
+      <x:c r="B7" s="564" t="str">
+        <x:v>language</x:v>
+      </x:c>
+      <x:c r="C7" s="564" t="str">
+        <x:v>question</x:v>
+      </x:c>
+      <x:c r="D7" s="564" t="str">
+        <x:v>proposed evidence summary</x:v>
+      </x:c>
+      <x:c r="E7" s="564" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="F7" s="564" t="str">
+        <x:v>human_relevant_chunk_ids</x:v>
+      </x:c>
+      <x:c r="G7" s="564" t="str">
+        <x:v>correction_notes</x:v>
+      </x:c>
+      <x:c r="H7" s="564" t="str">
+        <x:v>reviewer</x:v>
+      </x:c>
+      <x:c r="I7" s="565" t="str">
+        <x:v>reviewed_at</x:v>
+      </x:c>
+      <x:c r="K7" s="563" t="str">
+        <x:v>question_id</x:v>
+      </x:c>
+      <x:c r="L7" s="564" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="M7" s="564" t="str">
+        <x:v>human_relevant_chunk_ids</x:v>
+      </x:c>
+      <x:c r="N7" s="564" t="str">
+        <x:v>reviewer</x:v>
+      </x:c>
+      <x:c r="O7" s="564" t="str">
+        <x:v>reviewed_at</x:v>
+      </x:c>
+      <x:c r="P7" s="565" t="str">
+        <x:v>correction_notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="60" customHeight="1">
+      <x:c r="A8" s="599" t="str">
+        <x:v>gold30-001</x:v>
+      </x:c>
+      <x:c r="B8" s="574" t="str">
         <x:v>English</x:v>
       </x:c>
-      <x:c r="E7" s="39" t="n">
-        <x:f>COUNTIF('Review Queue'!$C$6:$C$35,D7)</x:f>
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G7" s="42" t="str">
-        <x:v>Documents</x:v>
-      </x:c>
-      <x:c r="H7" s="46" t="n">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="32" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="B8" s="36" t="n">
-        <x:f>COUNTIF('Review Queue'!$F$6:$F$35,"Approved")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="32" t="str">
+      <x:c r="C8" s="574" t="str">
+        <x:v>What is the latest PM2.5 reading for Jakarta Pusat, and when was it observed?</x:v>
+      </x:c>
+      <x:c r="D8" s="574" t="str">
+        <x:v>Sources: jakarta-monitoring. Proposed chunks: jakarta-monitoring:structure:0. The official station portal establishes that readings need a station, pollutant, value and timestamp; a current value must come from the measurement tool.</x:v>
+      </x:c>
+      <x:c r="E8" s="585" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F8" s="585" t="str"/>
+      <x:c r="G8" s="585" t="str"/>
+      <x:c r="H8" s="585" t="str"/>
+      <x:c r="I8" s="605" t="str"/>
+      <x:c r="K8" s="602" t="str">
+        <x:f>A8</x:f>
+        <x:v>gold30-001</x:v>
+      </x:c>
+      <x:c r="L8" s="596" t="str">
+        <x:f>E8</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M8" s="608" t="str">
+        <x:f>IF(F8="","",F8)</x:f>
+      </x:c>
+      <x:c r="N8" s="596" t="str">
+        <x:f>IF(H8="","",H8)</x:f>
+      </x:c>
+      <x:c r="O8" s="596" t="str">
+        <x:f>IF(I8="","",I8)</x:f>
+      </x:c>
+      <x:c r="P8" s="596" t="str">
+        <x:f>IF(G8="","",G8)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="60" customHeight="1">
+      <x:c r="A9" s="600" t="str">
+        <x:v>gold30-002</x:v>
+      </x:c>
+      <x:c r="B9" s="575" t="str">
         <x:v>Bahasa Indonesia</x:v>
       </x:c>
-      <x:c r="E8" s="39" t="n">
-        <x:f>COUNTIF('Review Queue'!$C$6:$C$35,D8)</x:f>
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G8" s="42" t="str">
-        <x:v>Chunks</x:v>
-      </x:c>
-      <x:c r="H8" s="46" t="n">
-        <x:v>113</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="32" t="str">
-        <x:v>Corrected</x:v>
-      </x:c>
-      <x:c r="B9" s="36" t="n">
-        <x:f>COUNTIF('Review Queue'!$F$6:$F$35,"Corrected")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="42" t="str">
-        <x:v>Corpus fingerprint</x:v>
-      </x:c>
-      <x:c r="H9" s="42" t="str">
-        <x:v>377ba2e4b26b2f8be68b4ec854d234fad27b11f7c9d0745fe2e04f1ff9b905a4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="32" t="str">
-        <x:v>Rejected</x:v>
-      </x:c>
-      <x:c r="B10" s="36" t="n">
-        <x:f>COUNTIF('Review Queue'!$F$6:$F$35,"Rejected")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="42" t="str">
-        <x:v>Report fingerprint</x:v>
-      </x:c>
-      <x:c r="H10" s="42" t="str">
-        <x:v>972c34481355f45f5b548fe5eca44e18a25f27a2244c471b287ee234691ba15d</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="32" t="str">
+      <x:c r="C9" s="575" t="str">
+        <x:v>Stasiun mana di Jakarta yang punya pembacaan ISPU terbaru paling tinggi?</x:v>
+      </x:c>
+      <x:c r="D9" s="575" t="str">
+        <x:v>Sources: jakarta-monitoring, ispu. Proposed chunks: jakarta-monitoring:structure:0, ispu:structure:0. Requires a current-station lookup plus the ISPU category interpretation; the corpus alone cannot substitute for a live observation.</x:v>
+      </x:c>
+      <x:c r="E9" s="586" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="B11" s="36" t="n">
-        <x:f>COUNTIF('Review Queue'!$F$6:$F$35,"Pending")</x:f>
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G11" s="42" t="str">
-        <x:v>Packet state</x:v>
-      </x:c>
-      <x:c r="H11" s="42" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="32" customHeight="1">
-      <x:c r="A14" s="28" t="str">
-        <x:v>Topic distribution</x:v>
-      </x:c>
-      <x:c r="B14" s="29" t="str">
-        <x:v>Count</x:v>
-      </x:c>
-      <x:c r="D14" s="28" t="str">
-        <x:v>Difficulty distribution</x:v>
-      </x:c>
-      <x:c r="E14" s="29" t="str">
-        <x:v>Count</x:v>
-      </x:c>
-      <x:c r="G14" s="28" t="str">
-        <x:v>How to review</x:v>
-      </x:c>
-      <x:c r="H14" s="29"/>
-    </x:row>
-    <x:row r="15" ht="26" customHeight="1">
-      <x:c r="A15" s="41" t="str">
-        <x:v>current_measurements</x:v>
-      </x:c>
-      <x:c r="B15" s="50" t="n">
-        <x:f>COUNTIF('Review Queue'!$D$6:$D$35,A15)</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D15" s="32" t="str">
-        <x:v>easy</x:v>
-      </x:c>
-      <x:c r="E15" s="39" t="n">
-        <x:f>COUNTIF('Review Queue'!$E$6:$E$35,D15)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G15" s="51" t="str">
-        <x:v>1. Filter Evidence by question_id and inspect the proposed passages.</x:v>
-      </x:c>
-      <x:c r="H15" s="51"/>
-    </x:row>
-    <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="41" t="str">
-        <x:v>historical_category_threshold</x:v>
-      </x:c>
-      <x:c r="B16" s="50" t="n">
-        <x:f>COUNTIF('Review Queue'!$D$6:$D$35,A16)</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D16" s="32" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="E16" s="39" t="n">
-        <x:f>COUNTIF('Review Queue'!$E$6:$E$35,D16)</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G16" s="51" t="str">
-        <x:v>2. Set Status to Approved, Corrected, or Rejected.</x:v>
-      </x:c>
-      <x:c r="H16" s="51"/>
-    </x:row>
-    <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="41" t="str">
-        <x:v>causes</x:v>
-      </x:c>
-      <x:c r="B17" s="50" t="n">
-        <x:f>COUNTIF('Review Queue'!$D$6:$D$35,A17)</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="32" t="str">
-        <x:v>hard</x:v>
-      </x:c>
-      <x:c r="E17" s="39" t="n">
-        <x:f>COUNTIF('Review Queue'!$E$6:$E$35,D17)</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G17" s="51" t="str">
-        <x:v>3. Enter exact human chunk IDs for Approved/Corrected.</x:v>
-      </x:c>
-      <x:c r="H17" s="51"/>
-    </x:row>
-    <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="41" t="str">
-        <x:v>regulations_implementation</x:v>
-      </x:c>
-      <x:c r="B18" s="50" t="n">
-        <x:f>COUNTIF('Review Queue'!$D$6:$D$35,A18)</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G18" s="51" t="str">
-        <x:v>4. Add reviewer, date, and correction notes.</x:v>
-      </x:c>
-      <x:c r="H18" s="51"/>
-    </x:row>
-    <x:row r="19" ht="26" customHeight="1">
-      <x:c r="A19" s="41" t="str">
-        <x:v>protection_individual_action</x:v>
-      </x:c>
-      <x:c r="B19" s="50" t="n">
-        <x:f>COUNTIF('Review Queue'!$D$6:$D$35,A19)</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G19" s="51" t="str">
-        <x:v>5. Export the six editable columns to CSV.</x:v>
-      </x:c>
-      <x:c r="H19" s="51"/>
-    </x:row>
-    <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="41" t="str">
-        <x:v>multi_turn_followups</x:v>
-      </x:c>
-      <x:c r="B20" s="50" t="n">
-        <x:f>COUNTIF('Review Queue'!$D$6:$D$35,A20)</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G20" s="51" t="str">
-        <x:v>6. Run evaluation/finalize_gold_review.py after all rows are decided.</x:v>
-      </x:c>
-      <x:c r="H20" s="51"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="41" t="str">
-        <x:v>missing_data_safety_abstention</x:v>
-      </x:c>
-      <x:c r="B21" s="50" t="n">
-        <x:f>COUNTIF('Review Queue'!$D$6:$D$35,A21)</x:f>
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="26" customHeight="1">
-      <x:c r="A23" s="54" t="str">
-        <x:v>The separate development pool contains 120 seeded rows. They are listed in the manifest and are not part of this focused queue.</x:v>
-      </x:c>
-      <x:c r="B23" s="54"/>
-      <x:c r="C23" s="54"/>
-      <x:c r="D23" s="54"/>
-      <x:c r="E23" s="54"/>
-      <x:c r="F23" s="54"/>
-      <x:c r="G23" s="54"/>
-      <x:c r="H23" s="54"/>
+      <x:c r="F9" s="586" t="str"/>
+      <x:c r="G9" s="586" t="str"/>
+      <x:c r="H9" s="586" t="str"/>
+      <x:c r="I9" s="606" t="str"/>
+      <x:c r="K9" s="603" t="str">
+        <x:f>A9</x:f>
+        <x:v>gold30-002</x:v>
+      </x:c>
+      <x:c r="L9" s="597" t="str">
+        <x:f>E9</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M9" s="609" t="str">
+        <x:f>IF(F9="","",F9)</x:f>
+      </x:c>
+      <x:c r="N9" s="597" t="str">
+        <x:f>IF(H9="","",H9)</x:f>
+      </x:c>
+      <x:c r="O9" s="597" t="str">
+        <x:f>IF(I9="","",I9)</x:f>
+      </x:c>
+      <x:c r="P9" s="597" t="str">
+        <x:f>IF(G9="","",G9)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="60" customHeight="1">
+      <x:c r="A10" s="600" t="str">
+        <x:v>gold30-003</x:v>
+      </x:c>
+      <x:c r="B10" s="575" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="C10" s="575" t="str">
+        <x:v>Is an ISPU of 125 a concentration of 125 µg/m³?</x:v>
+      </x:c>
+      <x:c r="D10" s="575" t="str">
+        <x:v>Sources: ispu. Proposed chunks: ispu:structure:0. The ISPU source explicitly separates the unitless index from a physical pollutant concentration.</x:v>
+      </x:c>
+      <x:c r="E10" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F10" s="586" t="str"/>
+      <x:c r="G10" s="586" t="str"/>
+      <x:c r="H10" s="586" t="str"/>
+      <x:c r="I10" s="606" t="str"/>
+      <x:c r="K10" s="603" t="str">
+        <x:f>A10</x:f>
+        <x:v>gold30-003</x:v>
+      </x:c>
+      <x:c r="L10" s="597" t="str">
+        <x:f>E10</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M10" s="609" t="str">
+        <x:f>IF(F10="","",F10)</x:f>
+      </x:c>
+      <x:c r="N10" s="597" t="str">
+        <x:f>IF(H10="","",H10)</x:f>
+      </x:c>
+      <x:c r="O10" s="597" t="str">
+        <x:f>IF(I10="","",I10)</x:f>
+      </x:c>
+      <x:c r="P10" s="597" t="str">
+        <x:f>IF(G10="","",G10)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="60" customHeight="1">
+      <x:c r="A11" s="600" t="str">
+        <x:v>gold30-004</x:v>
+      </x:c>
+      <x:c r="B11" s="575" t="str">
+        <x:v>Bahasa Indonesia</x:v>
+      </x:c>
+      <x:c r="C11" s="575" t="str">
+        <x:v>Tolong cek kualitas udara di Kepulauan Seribu—jika tidak ada data, apa yang bisa disimpulkan?</x:v>
+      </x:c>
+      <x:c r="D11" s="575" t="str">
+        <x:v>Sources: jakarta-monitoring. Proposed chunks: jakarta-monitoring:structure:0. This is a negative/no-result case: the answer should report absence of a matching observation rather than inventing a value; the portal source documents station scope.</x:v>
+      </x:c>
+      <x:c r="E11" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F11" s="586" t="str"/>
+      <x:c r="G11" s="586" t="str"/>
+      <x:c r="H11" s="586" t="str"/>
+      <x:c r="I11" s="606" t="str"/>
+      <x:c r="K11" s="603" t="str">
+        <x:f>A11</x:f>
+        <x:v>gold30-004</x:v>
+      </x:c>
+      <x:c r="L11" s="597" t="str">
+        <x:f>E11</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M11" s="609" t="str">
+        <x:f>IF(F11="","",F11)</x:f>
+      </x:c>
+      <x:c r="N11" s="597" t="str">
+        <x:f>IF(H11="","",H11)</x:f>
+      </x:c>
+      <x:c r="O11" s="597" t="str">
+        <x:f>IF(I11="","",I11)</x:f>
+      </x:c>
+      <x:c r="P11" s="597" t="str">
+        <x:f>IF(G11="","",G11)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="60" customHeight="1">
+      <x:c r="A12" s="600" t="str">
+        <x:v>gold30-005</x:v>
+      </x:c>
+      <x:c r="B12" s="575" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="C12" s="575" t="str">
+        <x:v>What does ISPU 45 mean, and how is that different from PM2.5 at 15 µg/m³?</x:v>
+      </x:c>
+      <x:c r="D12" s="575" t="str">
+        <x:v>Sources: ispu. Proposed chunks: ispu:structure:1. ISPU 45 is a category value, while PM2.5 is a concentration with units; the index source supports the distinction.</x:v>
+      </x:c>
+      <x:c r="E12" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F12" s="586" t="str"/>
+      <x:c r="G12" s="586" t="str"/>
+      <x:c r="H12" s="586" t="str"/>
+      <x:c r="I12" s="606" t="str"/>
+      <x:c r="K12" s="603" t="str">
+        <x:f>A12</x:f>
+        <x:v>gold30-005</x:v>
+      </x:c>
+      <x:c r="L12" s="597" t="str">
+        <x:f>E12</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M12" s="609" t="str">
+        <x:f>IF(F12="","",F12)</x:f>
+      </x:c>
+      <x:c r="N12" s="597" t="str">
+        <x:f>IF(H12="","",H12)</x:f>
+      </x:c>
+      <x:c r="O12" s="597" t="str">
+        <x:f>IF(I12="","",I12)</x:f>
+      </x:c>
+      <x:c r="P12" s="597" t="str">
+        <x:f>IF(G12="","",G12)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="60" customHeight="1">
+      <x:c r="A13" s="600" t="str">
+        <x:v>gold30-006</x:v>
+      </x:c>
+      <x:c r="B13" s="575" t="str">
+        <x:v>Bahasa Indonesia</x:v>
+      </x:c>
+      <x:c r="C13" s="575" t="str">
+        <x:v>Berapa pedoman WHO PM2.5 tahunan dan 24 jam, dan apakah itu ambang hukum Indonesia?</x:v>
+      </x:c>
+      <x:c r="D13" s="575" t="str">
+        <x:v>Sources: who-aqg-2021-extract, jakarta-regulations. Proposed chunks: who-aqg-2021-extract:structure:2, jakarta-regulations:structure:0. Needs complementary WHO numeric guidance and Indonesian legal-status context; neither source alone answers both parts.</x:v>
+      </x:c>
+      <x:c r="E13" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F13" s="586" t="str"/>
+      <x:c r="G13" s="586" t="str"/>
+      <x:c r="H13" s="586" t="str"/>
+      <x:c r="I13" s="606" t="str"/>
+      <x:c r="K13" s="603" t="str">
+        <x:f>A13</x:f>
+        <x:v>gold30-006</x:v>
+      </x:c>
+      <x:c r="L13" s="597" t="str">
+        <x:f>E13</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M13" s="609" t="str">
+        <x:f>IF(F13="","",F13)</x:f>
+      </x:c>
+      <x:c r="N13" s="597" t="str">
+        <x:f>IF(H13="","",H13)</x:f>
+      </x:c>
+      <x:c r="O13" s="597" t="str">
+        <x:f>IF(I13="","",I13)</x:f>
+      </x:c>
+      <x:c r="P13" s="597" t="str">
+        <x:f>IF(G13="","",G13)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="60" customHeight="1">
+      <x:c r="A14" s="600" t="str">
+        <x:v>gold30-007</x:v>
+      </x:c>
+      <x:c r="B14" s="575" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="C14" s="575" t="str">
+        <x:v>Did Jakarta's historical PM2.5 series come from station sensors or a model?</x:v>
+      </x:c>
+      <x:c r="D14" s="575" t="str">
+        <x:v>Sources: jakarta-historical-city-series. Proposed chunks: jakarta-historical-city-series:structure:2. The historical-series provenance notes CAMS/Open-Meteo model concentrations rather than DKI station measurements.</x:v>
+      </x:c>
+      <x:c r="E14" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F14" s="586" t="str"/>
+      <x:c r="G14" s="586" t="str"/>
+      <x:c r="H14" s="586" t="str"/>
+      <x:c r="I14" s="606" t="str"/>
+      <x:c r="K14" s="603" t="str">
+        <x:f>A14</x:f>
+        <x:v>gold30-007</x:v>
+      </x:c>
+      <x:c r="L14" s="597" t="str">
+        <x:f>E14</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M14" s="609" t="str">
+        <x:f>IF(F14="","",F14)</x:f>
+      </x:c>
+      <x:c r="N14" s="597" t="str">
+        <x:f>IF(H14="","",H14)</x:f>
+      </x:c>
+      <x:c r="O14" s="597" t="str">
+        <x:f>IF(I14="","",I14)</x:f>
+      </x:c>
+      <x:c r="P14" s="597" t="str">
+        <x:f>IF(G14="","",G14)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="60" customHeight="1">
+      <x:c r="A15" s="600" t="str">
+        <x:v>gold30-008</x:v>
+      </x:c>
+      <x:c r="B15" s="575" t="str">
+        <x:v>Bahasa Indonesia</x:v>
+      </x:c>
+      <x:c r="C15" s="575" t="str">
+        <x:v>Mengapa PM10 dan PM2.5 pada data historis dipisahkan?</x:v>
+      </x:c>
+      <x:c r="D15" s="575" t="str">
+        <x:v>Sources: jakarta-historical-city-series. Proposed chunks: jakarta-historical-city-series:structure:2. The series description defines PM10 and PM2.5 as separate pollutant variables with separate units and averaging.</x:v>
+      </x:c>
+      <x:c r="E15" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F15" s="586" t="str"/>
+      <x:c r="G15" s="586" t="str"/>
+      <x:c r="H15" s="586" t="str"/>
+      <x:c r="I15" s="606" t="str"/>
+      <x:c r="K15" s="603" t="str">
+        <x:f>A15</x:f>
+        <x:v>gold30-008</x:v>
+      </x:c>
+      <x:c r="L15" s="597" t="str">
+        <x:f>E15</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M15" s="609" t="str">
+        <x:f>IF(F15="","",F15)</x:f>
+      </x:c>
+      <x:c r="N15" s="597" t="str">
+        <x:f>IF(H15="","",H15)</x:f>
+      </x:c>
+      <x:c r="O15" s="597" t="str">
+        <x:f>IF(I15="","",I15)</x:f>
+      </x:c>
+      <x:c r="P15" s="597" t="str">
+        <x:f>IF(G15="","",G15)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="60" customHeight="1">
+      <x:c r="A16" s="600" t="str">
+        <x:v>gold30-009</x:v>
+      </x:c>
+      <x:c r="B16" s="575" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="C16" s="575" t="str">
+        <x:v>Can an ISPU category alone tell me whether the WHO annual guideline was met?</x:v>
+      </x:c>
+      <x:c r="D16" s="575" t="str">
+        <x:v>Sources: ispu, who-aqg-2021-extract. Proposed chunks: ispu:structure:0, who-aqg-2021-extract:structure:2. Requires keeping an index category, concentration, pollutant and averaging period distinct; complementary sources are needed.</x:v>
+      </x:c>
+      <x:c r="E16" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F16" s="586" t="str"/>
+      <x:c r="G16" s="586" t="str"/>
+      <x:c r="H16" s="586" t="str"/>
+      <x:c r="I16" s="606" t="str"/>
+      <x:c r="K16" s="603" t="str">
+        <x:f>A16</x:f>
+        <x:v>gold30-009</x:v>
+      </x:c>
+      <x:c r="L16" s="597" t="str">
+        <x:f>E16</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M16" s="609" t="str">
+        <x:f>IF(F16="","",F16)</x:f>
+      </x:c>
+      <x:c r="N16" s="597" t="str">
+        <x:f>IF(H16="","",H16)</x:f>
+      </x:c>
+      <x:c r="O16" s="597" t="str">
+        <x:f>IF(I16="","",I16)</x:f>
+      </x:c>
+      <x:c r="P16" s="597" t="str">
+        <x:f>IF(G16="","",G16)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="60" customHeight="1">
+      <x:c r="A17" s="600" t="str">
+        <x:v>gold30-010</x:v>
+      </x:c>
+      <x:c r="B17" s="575" t="str">
+        <x:v>Bahasa Indonesia</x:v>
+      </x:c>
+      <x:c r="C17" s="575" t="str">
+        <x:v>Sumber apa yang terkait dengan PM2.5 Jakarta, dan mengapa satu sumber tidak boleh langsung disebut penyebab pembacaan satu stasiun?</x:v>
+      </x:c>
+      <x:c r="D17" s="575" t="str">
+        <x:v>Sources: jakarta-causes. Proposed chunks: jakarta-causes:structure:0. The causes record distinguishes likely contributors and cautions against causal claims about a single timestamped station reading.</x:v>
+      </x:c>
+      <x:c r="E17" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F17" s="586" t="str"/>
+      <x:c r="G17" s="586" t="str"/>
+      <x:c r="H17" s="586" t="str"/>
+      <x:c r="I17" s="606" t="str"/>
+      <x:c r="K17" s="603" t="str">
+        <x:f>A17</x:f>
+        <x:v>gold30-010</x:v>
+      </x:c>
+      <x:c r="L17" s="597" t="str">
+        <x:f>E17</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M17" s="609" t="str">
+        <x:f>IF(F17="","",F17)</x:f>
+      </x:c>
+      <x:c r="N17" s="597" t="str">
+        <x:f>IF(H17="","",H17)</x:f>
+      </x:c>
+      <x:c r="O17" s="597" t="str">
+        <x:f>IF(I17="","",I17)</x:f>
+      </x:c>
+      <x:c r="P17" s="597" t="str">
+        <x:f>IF(G17="","",G17)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="60" customHeight="1">
+      <x:c r="A18" s="600" t="str">
+        <x:v>gold30-011</x:v>
+      </x:c>
+      <x:c r="B18" s="575" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="C18" s="575" t="str">
+        <x:v>What is the difference between an emissions inventory and source apportionment?</x:v>
+      </x:c>
+      <x:c r="D18" s="575" t="str">
+        <x:v>Sources: jakarta-causes. Proposed chunks: jakarta-causes:structure:1. The causes record explains the different methods and their interpretation limits.</x:v>
+      </x:c>
+      <x:c r="E18" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F18" s="586" t="str"/>
+      <x:c r="G18" s="586" t="str"/>
+      <x:c r="H18" s="586" t="str"/>
+      <x:c r="I18" s="606" t="str"/>
+      <x:c r="K18" s="603" t="str">
+        <x:f>A18</x:f>
+        <x:v>gold30-011</x:v>
+      </x:c>
+      <x:c r="L18" s="597" t="str">
+        <x:f>E18</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M18" s="609" t="str">
+        <x:f>IF(F18="","",F18)</x:f>
+      </x:c>
+      <x:c r="N18" s="597" t="str">
+        <x:f>IF(H18="","",H18)</x:f>
+      </x:c>
+      <x:c r="O18" s="597" t="str">
+        <x:f>IF(I18="","",I18)</x:f>
+      </x:c>
+      <x:c r="P18" s="597" t="str">
+        <x:f>IF(G18="","",G18)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="60" customHeight="1">
+      <x:c r="A19" s="600" t="str">
+        <x:v>gold30-012</x:v>
+      </x:c>
+      <x:c r="B19" s="575" t="str">
+        <x:v>Bahasa Indonesia</x:v>
+      </x:c>
+      <x:c r="C19" s="575" t="str">
+        <x:v>Apakah pembacaan tinggi di jalan saya membuktikan pabrik menjadi penyebabnya?</x:v>
+      </x:c>
+      <x:c r="D19" s="575" t="str">
+        <x:v>Sources: jakarta-causes. Proposed chunks: jakarta-causes:structure:0. Ambiguous causal question; the source supports multiple contributors and explicitly rejects assigning one cause to one reading without local evidence.</x:v>
+      </x:c>
+      <x:c r="E19" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F19" s="586" t="str"/>
+      <x:c r="G19" s="586" t="str"/>
+      <x:c r="H19" s="586" t="str"/>
+      <x:c r="I19" s="606" t="str"/>
+      <x:c r="K19" s="603" t="str">
+        <x:f>A19</x:f>
+        <x:v>gold30-012</x:v>
+      </x:c>
+      <x:c r="L19" s="597" t="str">
+        <x:f>E19</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M19" s="609" t="str">
+        <x:f>IF(F19="","",F19)</x:f>
+      </x:c>
+      <x:c r="N19" s="597" t="str">
+        <x:f>IF(H19="","",H19)</x:f>
+      </x:c>
+      <x:c r="O19" s="597" t="str">
+        <x:f>IF(I19="","",I19)</x:f>
+      </x:c>
+      <x:c r="P19" s="597" t="str">
+        <x:f>IF(G19="","",G19)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="60" customHeight="1">
+      <x:c r="A20" s="600" t="str">
+        <x:v>gold30-013</x:v>
+      </x:c>
+      <x:c r="B20" s="575" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="C20" s="575" t="str">
+        <x:v>Does Jakarta's air pollution come only from inside the city?</x:v>
+      </x:c>
+      <x:c r="D20" s="575" t="str">
+        <x:v>Sources: jakarta-causes, jakarta-policy-implementation. Proposed chunks: jakarta-causes:structure:0, jakarta-policy-implementation:structure:2. Needs the causes discussion of local and regional sources and the implementation record's airshed/coordination context.</x:v>
+      </x:c>
+      <x:c r="E20" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F20" s="586" t="str"/>
+      <x:c r="G20" s="586" t="str"/>
+      <x:c r="H20" s="586" t="str"/>
+      <x:c r="I20" s="606" t="str"/>
+      <x:c r="K20" s="603" t="str">
+        <x:f>A20</x:f>
+        <x:v>gold30-013</x:v>
+      </x:c>
+      <x:c r="L20" s="597" t="str">
+        <x:f>E20</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M20" s="609" t="str">
+        <x:f>IF(F20="","",F20)</x:f>
+      </x:c>
+      <x:c r="N20" s="597" t="str">
+        <x:f>IF(H20="","",H20)</x:f>
+      </x:c>
+      <x:c r="O20" s="597" t="str">
+        <x:f>IF(I20="","",I20)</x:f>
+      </x:c>
+      <x:c r="P20" s="597" t="str">
+        <x:f>IF(G20="","",G20)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="60" customHeight="1">
+      <x:c r="A21" s="600" t="str">
+        <x:v>gold30-014</x:v>
+      </x:c>
+      <x:c r="B21" s="575" t="str">
+        <x:v>Bahasa Indonesia</x:v>
+      </x:c>
+      <x:c r="C21" s="575" t="str">
+        <x:v>Apakah Pergub 66/2020 masih tercatat berlaku, dan apa yang dibuktikannya tentang penegakan?</x:v>
+      </x:c>
+      <x:c r="D21" s="575" t="str">
+        <x:v>Sources: pergub-66-2020-vehicle-testing, jakarta-emission-testing. Proposed chunks: pergub-66-2020-vehicle-testing:structure:0, jakarta-emission-testing:structure:0. Separates legal status from evidence of enforcement; the legal record and DKI FAQ provide complementary context.</x:v>
+      </x:c>
+      <x:c r="E21" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F21" s="586" t="str"/>
+      <x:c r="G21" s="586" t="str"/>
+      <x:c r="H21" s="586" t="str"/>
+      <x:c r="I21" s="606" t="str"/>
+      <x:c r="K21" s="603" t="str">
+        <x:f>A21</x:f>
+        <x:v>gold30-014</x:v>
+      </x:c>
+      <x:c r="L21" s="597" t="str">
+        <x:f>E21</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M21" s="609" t="str">
+        <x:f>IF(F21="","",F21)</x:f>
+      </x:c>
+      <x:c r="N21" s="597" t="str">
+        <x:f>IF(H21="","",H21)</x:f>
+      </x:c>
+      <x:c r="O21" s="597" t="str">
+        <x:f>IF(I21="","",I21)</x:f>
+      </x:c>
+      <x:c r="P21" s="597" t="str">
+        <x:f>IF(G21="","",G21)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="60" customHeight="1">
+      <x:c r="A22" s="600" t="str">
+        <x:v>gold30-015</x:v>
+      </x:c>
+      <x:c r="B22" s="575" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="C22" s="575" t="str">
+        <x:v>Which vehicle categories and ages are covered by Permen LHK 8/2023?</x:v>
+      </x:c>
+      <x:c r="D22" s="575" t="str">
+        <x:v>Sources: permen-lhk-8-2023-vehicle-emissions. Proposed chunks: permen-lhk-8-2023-vehicle-emissions:structure:0. The official abstract states categories M, N, O and L and the more-than-three-years condition.</x:v>
+      </x:c>
+      <x:c r="E22" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F22" s="586" t="str"/>
+      <x:c r="G22" s="586" t="str"/>
+      <x:c r="H22" s="586" t="str"/>
+      <x:c r="I22" s="606" t="str"/>
+      <x:c r="K22" s="603" t="str">
+        <x:f>A22</x:f>
+        <x:v>gold30-015</x:v>
+      </x:c>
+      <x:c r="L22" s="597" t="str">
+        <x:f>E22</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M22" s="609" t="str">
+        <x:f>IF(F22="","",F22)</x:f>
+      </x:c>
+      <x:c r="N22" s="597" t="str">
+        <x:f>IF(H22="","",H22)</x:f>
+      </x:c>
+      <x:c r="O22" s="597" t="str">
+        <x:f>IF(I22="","",I22)</x:f>
+      </x:c>
+      <x:c r="P22" s="597" t="str">
+        <x:f>IF(G22="","",G22)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="60" customHeight="1">
+      <x:c r="A23" s="600" t="str">
+        <x:v>gold30-016</x:v>
+      </x:c>
+      <x:c r="B23" s="575" t="str">
+        <x:v>Bahasa Indonesia</x:v>
+      </x:c>
+      <x:c r="C23" s="575" t="str">
+        <x:v>Apakah konektivitas CEMS menunjukkan bahwa setiap cerobong sudah memenuhi batas emisi?</x:v>
+      </x:c>
+      <x:c r="D23" s="575" t="str">
+        <x:v>Sources: permen-lhk-13-2021-cems, jakarta-cems-monitoring. Proposed chunks: permen-lhk-13-2021-cems:structure:0, jakarta-cems-monitoring:structure:1. Requires the regulation's CEMS boundary and the DKI monitoring-programme caveat that connectivity is not compliance proof.</x:v>
+      </x:c>
+      <x:c r="E23" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F23" s="586" t="str"/>
+      <x:c r="G23" s="586" t="str"/>
+      <x:c r="H23" s="586" t="str"/>
+      <x:c r="I23" s="606" t="str"/>
+      <x:c r="K23" s="603" t="str">
+        <x:f>A23</x:f>
+        <x:v>gold30-016</x:v>
+      </x:c>
+      <x:c r="L23" s="597" t="str">
+        <x:f>E23</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M23" s="609" t="str">
+        <x:f>IF(F23="","",F23)</x:f>
+      </x:c>
+      <x:c r="N23" s="597" t="str">
+        <x:f>IF(H23="","",H23)</x:f>
+      </x:c>
+      <x:c r="O23" s="597" t="str">
+        <x:f>IF(I23="","",I23)</x:f>
+      </x:c>
+      <x:c r="P23" s="597" t="str">
+        <x:f>IF(G23="","",G23)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="60" customHeight="1">
+      <x:c r="A24" s="600" t="str">
+        <x:v>gold30-017</x:v>
+      </x:c>
+      <x:c r="B24" s="575" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="C24" s="575" t="str">
+        <x:v>What does the Jakarta air-pollution court record establish, and does it prove every order was implemented?</x:v>
+      </x:c>
+      <x:c r="D24" s="575" t="str">
+        <x:v>Sources: jakarta-court-air-quality, ma-jakarta-air-lawsuit-record. Proposed chunks: jakarta-court-air-quality:structure:1, ma-jakarta-air-lawsuit-record:structure:1. Court-record identity and execution status are separate questions; both normalized records state that implementation needs later verification.</x:v>
+      </x:c>
+      <x:c r="E24" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F24" s="586" t="str"/>
+      <x:c r="G24" s="586" t="str"/>
+      <x:c r="H24" s="586" t="str"/>
+      <x:c r="I24" s="606" t="str"/>
+      <x:c r="K24" s="603" t="str">
+        <x:f>A24</x:f>
+        <x:v>gold30-017</x:v>
+      </x:c>
+      <x:c r="L24" s="597" t="str">
+        <x:f>E24</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M24" s="609" t="str">
+        <x:f>IF(F24="","",F24)</x:f>
+      </x:c>
+      <x:c r="N24" s="597" t="str">
+        <x:f>IF(H24="","",H24)</x:f>
+      </x:c>
+      <x:c r="O24" s="597" t="str">
+        <x:f>IF(I24="","",I24)</x:f>
+      </x:c>
+      <x:c r="P24" s="597" t="str">
+        <x:f>IF(G24="","",G24)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="60" customHeight="1">
+      <x:c r="A25" s="600" t="str">
+        <x:v>gold30-018</x:v>
+      </x:c>
+      <x:c r="B25" s="575" t="str">
+        <x:v>Bahasa Indonesia</x:v>
+      </x:c>
+      <x:c r="C25" s="575" t="str">
+        <x:v>Mengapa aturan dapat tetap ada sementara kualitas udara Jakarta masih buruk?</x:v>
+      </x:c>
+      <x:c r="D25" s="575" t="str">
+        <x:v>Sources: jakarta-policy-implementation, jakarta-regulations, jakarta-court-air-quality. Proposed chunks: jakarta-policy-implementation:structure:0, jakarta-regulations:structure:0, jakarta-court-air-quality:structure:1. Complementary rule-on-paper, implementation-gap and court context are required for a cautious explanation.</x:v>
+      </x:c>
+      <x:c r="E25" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F25" s="586" t="str"/>
+      <x:c r="G25" s="586" t="str"/>
+      <x:c r="H25" s="586" t="str"/>
+      <x:c r="I25" s="606" t="str"/>
+      <x:c r="K25" s="603" t="str">
+        <x:f>A25</x:f>
+        <x:v>gold30-018</x:v>
+      </x:c>
+      <x:c r="L25" s="597" t="str">
+        <x:f>E25</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M25" s="609" t="str">
+        <x:f>IF(F25="","",F25)</x:f>
+      </x:c>
+      <x:c r="N25" s="597" t="str">
+        <x:f>IF(H25="","",H25)</x:f>
+      </x:c>
+      <x:c r="O25" s="597" t="str">
+        <x:f>IF(I25="","",I25)</x:f>
+      </x:c>
+      <x:c r="P25" s="597" t="str">
+        <x:f>IF(G25="","",G25)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="60" customHeight="1">
+      <x:c r="A26" s="600" t="str">
+        <x:v>gold30-019</x:v>
+      </x:c>
+      <x:c r="B26" s="575" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="C26" s="575" t="str">
+        <x:v>What should I do on a bad-air day, and do masks replace clean-air policy?</x:v>
+      </x:c>
+      <x:c r="D26" s="575" t="str">
+        <x:v>Sources: bad-air-day-protection, exposure-protection. Proposed chunks: bad-air-day-protection:structure:3, exposure-protection:structure:1. The health guidance covers immediate exposure reduction and the explicit limit that personal protection cannot replace emissions policy.</x:v>
+      </x:c>
+      <x:c r="E26" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F26" s="586" t="str"/>
+      <x:c r="G26" s="586" t="str"/>
+      <x:c r="H26" s="586" t="str"/>
+      <x:c r="I26" s="606" t="str"/>
+      <x:c r="K26" s="603" t="str">
+        <x:f>A26</x:f>
+        <x:v>gold30-019</x:v>
+      </x:c>
+      <x:c r="L26" s="597" t="str">
+        <x:f>E26</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M26" s="609" t="str">
+        <x:f>IF(F26="","",F26)</x:f>
+      </x:c>
+      <x:c r="N26" s="597" t="str">
+        <x:f>IF(H26="","",H26)</x:f>
+      </x:c>
+      <x:c r="O26" s="597" t="str">
+        <x:f>IF(I26="","",I26)</x:f>
+      </x:c>
+      <x:c r="P26" s="597" t="str">
+        <x:f>IF(G26="","",G26)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="60" customHeight="1">
+      <x:c r="A27" s="600" t="str">
+        <x:v>gold30-020</x:v>
+      </x:c>
+      <x:c r="B27" s="575" t="str">
+        <x:v>Bahasa Indonesia</x:v>
+      </x:c>
+      <x:c r="C27" s="575" t="str">
+        <x:v>Bagaimana memilih pembersih udara untuk kamar 20 m², dan apa batasannya?</x:v>
+      </x:c>
+      <x:c r="D27" s="575" t="str">
+        <x:v>Sources: clean-air-room. Proposed chunks: clean-air-room:structure:0. The EPA-derived room-sizing and limitation guidance supports a cautious engineering answer, not a local health guarantee.</x:v>
+      </x:c>
+      <x:c r="E27" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F27" s="586" t="str"/>
+      <x:c r="G27" s="586" t="str"/>
+      <x:c r="H27" s="586" t="str"/>
+      <x:c r="I27" s="606" t="str"/>
+      <x:c r="K27" s="603" t="str">
+        <x:f>A27</x:f>
+        <x:v>gold30-020</x:v>
+      </x:c>
+      <x:c r="L27" s="597" t="str">
+        <x:f>E27</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M27" s="609" t="str">
+        <x:f>IF(F27="","",F27)</x:f>
+      </x:c>
+      <x:c r="N27" s="597" t="str">
+        <x:f>IF(H27="","",H27)</x:f>
+      </x:c>
+      <x:c r="O27" s="597" t="str">
+        <x:f>IF(I27="","",I27)</x:f>
+      </x:c>
+      <x:c r="P27" s="597" t="str">
+        <x:f>IF(G27="","",G27)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="60" customHeight="1">
+      <x:c r="A28" s="600" t="str">
+        <x:v>gold30-021</x:v>
+      </x:c>
+      <x:c r="B28" s="575" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="C28" s="575" t="str">
+        <x:v>Is an N95-style particulate respirator protection against every pollutant?</x:v>
+      </x:c>
+      <x:c r="D28" s="575" t="str">
+        <x:v>Sources: who-personal-interventions-2024, exposure-protection. Proposed chunks: who-personal-interventions-2024:structure:3, exposure-protection:structure:1. The guidance supports particulate protection with fit caveats and says respirators do not filter every gas.</x:v>
+      </x:c>
+      <x:c r="E28" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F28" s="586" t="str"/>
+      <x:c r="G28" s="586" t="str"/>
+      <x:c r="H28" s="586" t="str"/>
+      <x:c r="I28" s="606" t="str"/>
+      <x:c r="K28" s="603" t="str">
+        <x:f>A28</x:f>
+        <x:v>gold30-021</x:v>
+      </x:c>
+      <x:c r="L28" s="597" t="str">
+        <x:f>E28</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M28" s="609" t="str">
+        <x:f>IF(F28="","",F28)</x:f>
+      </x:c>
+      <x:c r="N28" s="597" t="str">
+        <x:f>IF(H28="","",H28)</x:f>
+      </x:c>
+      <x:c r="O28" s="597" t="str">
+        <x:f>IF(I28="","",I28)</x:f>
+      </x:c>
+      <x:c r="P28" s="597" t="str">
+        <x:f>IF(G28="","",G28)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="60" customHeight="1">
+      <x:c r="A29" s="600" t="str">
+        <x:v>gold30-022</x:v>
+      </x:c>
+      <x:c r="B29" s="575" t="str">
+        <x:v>Bahasa Indonesia</x:v>
+      </x:c>
+      <x:c r="C29" s="575" t="str">
+        <x:v>Apa yang bisa saya lakukan untuk mengurangi emisi dan melaporkan kendaraan berasap?</x:v>
+      </x:c>
+      <x:c r="D29" s="575" t="str">
+        <x:v>Sources: individual-emission-actions. Proposed chunks: individual-emission-actions:structure:0. The civic-actions source covers lower-emission travel, vehicle maintenance and evidence-preserving reports.</x:v>
+      </x:c>
+      <x:c r="E29" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F29" s="586" t="str"/>
+      <x:c r="G29" s="586" t="str"/>
+      <x:c r="H29" s="586" t="str"/>
+      <x:c r="I29" s="606" t="str"/>
+      <x:c r="K29" s="603" t="str">
+        <x:f>A29</x:f>
+        <x:v>gold30-022</x:v>
+      </x:c>
+      <x:c r="L29" s="597" t="str">
+        <x:f>E29</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M29" s="609" t="str">
+        <x:f>IF(F29="","",F29)</x:f>
+      </x:c>
+      <x:c r="N29" s="597" t="str">
+        <x:f>IF(H29="","",H29)</x:f>
+      </x:c>
+      <x:c r="O29" s="597" t="str">
+        <x:f>IF(I29="","",I29)</x:f>
+      </x:c>
+      <x:c r="P29" s="597" t="str">
+        <x:f>IF(G29="","",G29)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="60" customHeight="1">
+      <x:c r="A30" s="600" t="str">
+        <x:v>gold30-023</x:v>
+      </x:c>
+      <x:c r="B30" s="575" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="C30" s="575" t="str">
+        <x:v>Does staying indoors always reduce exposure during a pollution episode?</x:v>
+      </x:c>
+      <x:c r="D30" s="575" t="str">
+        <x:v>Sources: exposure-protection, clean-air-room, bad-air-day-protection. Proposed chunks: exposure-protection:structure:0, clean-air-room:structure:3, bad-air-day-protection:structure:0. Hard boundary case: indoors helps only when indoor air is cleaner and indoor sources, filtration, ventilation and infiltration are considered.</x:v>
+      </x:c>
+      <x:c r="E30" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F30" s="586" t="str"/>
+      <x:c r="G30" s="586" t="str"/>
+      <x:c r="H30" s="586" t="str"/>
+      <x:c r="I30" s="606" t="str"/>
+      <x:c r="K30" s="603" t="str">
+        <x:f>A30</x:f>
+        <x:v>gold30-023</x:v>
+      </x:c>
+      <x:c r="L30" s="597" t="str">
+        <x:f>E30</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M30" s="609" t="str">
+        <x:f>IF(F30="","",F30)</x:f>
+      </x:c>
+      <x:c r="N30" s="597" t="str">
+        <x:f>IF(H30="","",H30)</x:f>
+      </x:c>
+      <x:c r="O30" s="597" t="str">
+        <x:f>IF(I30="","",I30)</x:f>
+      </x:c>
+      <x:c r="P30" s="597" t="str">
+        <x:f>IF(G30="","",G30)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="60" customHeight="1">
+      <x:c r="A31" s="600" t="str">
+        <x:v>gold30-024</x:v>
+      </x:c>
+      <x:c r="B31" s="575" t="str">
+        <x:v>Bahasa Indonesia</x:v>
+      </x:c>
+      <x:c r="C31" s="575" t="str">
+        <x:v>Apa perbedaan aturan kualitas udara Jakarta yang berlaku dengan pedoman WHO?</x:v>
+      </x:c>
+      <x:c r="D31" s="575" t="str">
+        <x:v>Sources: jakarta-regulations, who-aqg-2021-extract. Proposed chunks: jakarta-regulations:structure:0, who-aqg-2021-extract:structure:1. Follow-up inherits the regulation context and asks for a law-versus-guideline distinction using complementary sources.</x:v>
+      </x:c>
+      <x:c r="E31" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F31" s="586" t="str"/>
+      <x:c r="G31" s="586" t="str"/>
+      <x:c r="H31" s="586" t="str"/>
+      <x:c r="I31" s="606" t="str"/>
+      <x:c r="K31" s="603" t="str">
+        <x:f>A31</x:f>
+        <x:v>gold30-024</x:v>
+      </x:c>
+      <x:c r="L31" s="597" t="str">
+        <x:f>E31</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M31" s="609" t="str">
+        <x:f>IF(F31="","",F31)</x:f>
+      </x:c>
+      <x:c r="N31" s="597" t="str">
+        <x:f>IF(H31="","",H31)</x:f>
+      </x:c>
+      <x:c r="O31" s="597" t="str">
+        <x:f>IF(I31="","",I31)</x:f>
+      </x:c>
+      <x:c r="P31" s="597" t="str">
+        <x:f>IF(G31="","",G31)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="60" customHeight="1">
+      <x:c r="A32" s="600" t="str">
+        <x:v>gold30-025</x:v>
+      </x:c>
+      <x:c r="B32" s="575" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="C32" s="575" t="str">
+        <x:v>Does Jakarta Utara being categorized as Good most recently mean the air was safe all day?</x:v>
+      </x:c>
+      <x:c r="D32" s="575" t="str">
+        <x:v>Sources: jakarta-monitoring, ispu, health-disclaimer. Proposed chunks: jakarta-monitoring:structure:0, ispu:structure:0, health-disclaimer:structure:0. Follow-up must preserve timestamp/category limits and avoid converting one observation into an all-day or medical conclusion.</x:v>
+      </x:c>
+      <x:c r="E32" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F32" s="586" t="str"/>
+      <x:c r="G32" s="586" t="str"/>
+      <x:c r="H32" s="586" t="str"/>
+      <x:c r="I32" s="606" t="str"/>
+      <x:c r="K32" s="603" t="str">
+        <x:f>A32</x:f>
+        <x:v>gold30-025</x:v>
+      </x:c>
+      <x:c r="L32" s="597" t="str">
+        <x:f>E32</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M32" s="609" t="str">
+        <x:f>IF(F32="","",F32)</x:f>
+      </x:c>
+      <x:c r="N32" s="597" t="str">
+        <x:f>IF(H32="","",H32)</x:f>
+      </x:c>
+      <x:c r="O32" s="597" t="str">
+        <x:f>IF(I32="","",I32)</x:f>
+      </x:c>
+      <x:c r="P32" s="597" t="str">
+        <x:f>IF(G32="","",G32)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="60" customHeight="1">
+      <x:c r="A33" s="600" t="str">
+        <x:v>gold30-026</x:v>
+      </x:c>
+      <x:c r="B33" s="575" t="str">
+        <x:v>Bahasa Indonesia</x:v>
+      </x:c>
+      <x:c r="C33" s="575" t="str">
+        <x:v>Bisakah Anda membandingkan PM2.5 Jakarta Pusat dengan pedoman WHO 24 jam sambil mempertahankan waktu pengamatan dan satuannya?</x:v>
+      </x:c>
+      <x:c r="D33" s="575" t="str">
+        <x:v>Sources: jakarta-monitoring, who-aqg-2021-extract. Proposed chunks: jakarta-monitoring:structure:0, who-aqg-2021-extract:structure:2. Requires a current measurement tool result plus WHO's 24-hour value while preserving timestamp, pollutant and units.</x:v>
+      </x:c>
+      <x:c r="E33" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F33" s="586" t="str"/>
+      <x:c r="G33" s="586" t="str"/>
+      <x:c r="H33" s="586" t="str"/>
+      <x:c r="I33" s="606" t="str"/>
+      <x:c r="K33" s="603" t="str">
+        <x:f>A33</x:f>
+        <x:v>gold30-026</x:v>
+      </x:c>
+      <x:c r="L33" s="597" t="str">
+        <x:f>E33</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M33" s="609" t="str">
+        <x:f>IF(F33="","",F33)</x:f>
+      </x:c>
+      <x:c r="N33" s="597" t="str">
+        <x:f>IF(H33="","",H33)</x:f>
+      </x:c>
+      <x:c r="O33" s="597" t="str">
+        <x:f>IF(I33="","",I33)</x:f>
+      </x:c>
+      <x:c r="P33" s="597" t="str">
+        <x:f>IF(G33="","",G33)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="60" customHeight="1">
+      <x:c r="A34" s="600" t="str">
+        <x:v>gold30-027</x:v>
+      </x:c>
+      <x:c r="B34" s="575" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="C34" s="575" t="str">
+        <x:v>So does that mean vehicles definitely caused my station's reading today?</x:v>
+      </x:c>
+      <x:c r="D34" s="575" t="str">
+        <x:v>Sources: jakarta-causes, jakarta-monitoring. Proposed chunks: jakarta-causes:structure:2, jakarta-monitoring:structure:0. Follow-up tests whether likely contributors are incorrectly turned into proof of a single reading's cause.</x:v>
+      </x:c>
+      <x:c r="E34" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F34" s="586" t="str"/>
+      <x:c r="G34" s="586" t="str"/>
+      <x:c r="H34" s="586" t="str"/>
+      <x:c r="I34" s="606" t="str"/>
+      <x:c r="K34" s="603" t="str">
+        <x:f>A34</x:f>
+        <x:v>gold30-027</x:v>
+      </x:c>
+      <x:c r="L34" s="597" t="str">
+        <x:f>E34</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M34" s="609" t="str">
+        <x:f>IF(F34="","",F34)</x:f>
+      </x:c>
+      <x:c r="N34" s="597" t="str">
+        <x:f>IF(H34="","",H34)</x:f>
+      </x:c>
+      <x:c r="O34" s="597" t="str">
+        <x:f>IF(I34="","",I34)</x:f>
+      </x:c>
+      <x:c r="P34" s="597" t="str">
+        <x:f>IF(G34="","",G34)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="60" customHeight="1">
+      <x:c r="A35" s="600" t="str">
+        <x:v>gold30-028</x:v>
+      </x:c>
+      <x:c r="B35" s="575" t="str">
+        <x:v>Bahasa Indonesia</x:v>
+      </x:c>
+      <x:c r="C35" s="575" t="str">
+        <x:v>Bisakah informasi ini mendiagnosis apakah sesak dada saya disebabkan polusi udara?</x:v>
+      </x:c>
+      <x:c r="D35" s="575" t="str">
+        <x:v>Sources: health-disclaimer. Proposed chunks: health-disclaimer:structure:0. The health boundary explicitly says air-quality information is educational and does not diagnose an individual; severe or persistent symptoms need care.</x:v>
+      </x:c>
+      <x:c r="E35" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F35" s="586" t="str"/>
+      <x:c r="G35" s="586" t="str"/>
+      <x:c r="H35" s="586" t="str"/>
+      <x:c r="I35" s="606" t="str"/>
+      <x:c r="K35" s="603" t="str">
+        <x:f>A35</x:f>
+        <x:v>gold30-028</x:v>
+      </x:c>
+      <x:c r="L35" s="597" t="str">
+        <x:f>E35</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M35" s="609" t="str">
+        <x:f>IF(F35="","",F35)</x:f>
+      </x:c>
+      <x:c r="N35" s="597" t="str">
+        <x:f>IF(H35="","",H35)</x:f>
+      </x:c>
+      <x:c r="O35" s="597" t="str">
+        <x:f>IF(I35="","",I35)</x:f>
+      </x:c>
+      <x:c r="P35" s="597" t="str">
+        <x:f>IF(G35="","",G35)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="60" customHeight="1">
+      <x:c r="A36" s="600" t="str">
+        <x:v>gold30-029</x:v>
+      </x:c>
+      <x:c r="B36" s="575" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="C36" s="575" t="str">
+        <x:v>The station's PM2.5 value is blank; can you fill it with Jakarta's average?</x:v>
+      </x:c>
+      <x:c r="D36" s="575" t="str">
+        <x:v>Sources: jakarta-monitoring. Proposed chunks: jakarta-monitoring:structure:0. Negative-data case: a missing station value must not be replaced with an unrelated average; the portal provides provenance requirements.</x:v>
+      </x:c>
+      <x:c r="E36" s="586" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F36" s="586" t="str"/>
+      <x:c r="G36" s="586" t="str"/>
+      <x:c r="H36" s="586" t="str"/>
+      <x:c r="I36" s="606" t="str"/>
+      <x:c r="K36" s="603" t="str">
+        <x:f>A36</x:f>
+        <x:v>gold30-029</x:v>
+      </x:c>
+      <x:c r="L36" s="597" t="str">
+        <x:f>E36</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M36" s="609" t="str">
+        <x:f>IF(F36="","",F36)</x:f>
+      </x:c>
+      <x:c r="N36" s="597" t="str">
+        <x:f>IF(H36="","",H36)</x:f>
+      </x:c>
+      <x:c r="O36" s="597" t="str">
+        <x:f>IF(I36="","",I36)</x:f>
+      </x:c>
+      <x:c r="P36" s="597" t="str">
+        <x:f>IF(G36="","",G36)</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="60" customHeight="1">
+      <x:c r="A37" s="601" t="str">
+        <x:v>gold30-030</x:v>
+      </x:c>
+      <x:c r="B37" s="576" t="str">
+        <x:v>Bahasa Indonesia</x:v>
+      </x:c>
+      <x:c r="C37" s="576" t="str">
+        <x:v>Ringkasan putusan tidak punya tanggal penyelesaian; bolehkah kita mengatakan perintahnya sudah dilaksanakan?</x:v>
+      </x:c>
+      <x:c r="D37" s="576" t="str">
+        <x:v>Sources: ma-jakarta-air-lawsuit-record, jakarta-policy-implementation. Proposed chunks: ma-jakarta-air-lawsuit-record:structure:0, jakarta-policy-implementation:structure:0. The court record explicitly withholds completion claims without subsequent execution evidence.</x:v>
+      </x:c>
+      <x:c r="E37" s="587" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="F37" s="587" t="str"/>
+      <x:c r="G37" s="587" t="str"/>
+      <x:c r="H37" s="587" t="str"/>
+      <x:c r="I37" s="607" t="str"/>
+      <x:c r="K37" s="604" t="str">
+        <x:f>A37</x:f>
+        <x:v>gold30-030</x:v>
+      </x:c>
+      <x:c r="L37" s="598" t="str">
+        <x:f>E37</x:f>
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="M37" s="610" t="str">
+        <x:f>IF(F37="","",F37)</x:f>
+      </x:c>
+      <x:c r="N37" s="598" t="str">
+        <x:f>IF(H37="","",H37)</x:f>
+      </x:c>
+      <x:c r="O37" s="598" t="str">
+        <x:f>IF(I37="","",I37)</x:f>
+      </x:c>
+      <x:c r="P37" s="598" t="str">
+        <x:f>IF(G37="","",G37)</x:f>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
-    <x:mergeCell ref="A4:H4"/>
-    <x:mergeCell ref="G14:H14"/>
-    <x:mergeCell ref="G15:H15"/>
-    <x:mergeCell ref="G16:H16"/>
-    <x:mergeCell ref="G17:H17"/>
-    <x:mergeCell ref="G18:H18"/>
-    <x:mergeCell ref="G19:H19"/>
-    <x:mergeCell ref="G20:H20"/>
-    <x:mergeCell ref="A23:H23"/>
+    <x:mergeCell ref="A1:P1"/>
+    <x:mergeCell ref="A2:P2"/>
+    <x:mergeCell ref="A4:I4"/>
+    <x:mergeCell ref="A5:I5"/>
+    <x:mergeCell ref="K4:P4"/>
+    <x:mergeCell ref="K5:P5"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="E8:E37">
+    <x:cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Pending"/>
+    <x:cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Approved"/>
+    <x:cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="Corrected"/>
+    <x:cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="Rejected"/>
+    <x:cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="Pending"/>
+    <x:cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="Approved"/>
+    <x:cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="Corrected"/>
+    <x:cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="Rejected"/>
+    <x:cfRule type="containsText" dxfId="11" priority="9" operator="containsText" text="Pending"/>
+    <x:cfRule type="containsText" dxfId="12" priority="10" operator="containsText" text="Approved"/>
+    <x:cfRule type="containsText" dxfId="13" priority="11" operator="containsText" text="Corrected"/>
+    <x:cfRule type="containsText" dxfId="14" priority="12" operator="containsText" text="Rejected"/>
+    <x:cfRule type="containsText" dxfId="15" priority="13" operator="containsText" text="Pending"/>
+    <x:cfRule type="containsText" dxfId="16" priority="14" operator="containsText" text="Approved"/>
+    <x:cfRule type="containsText" dxfId="17" priority="15" operator="containsText" text="Corrected"/>
+    <x:cfRule type="containsText" dxfId="18" priority="16" operator="containsText" text="Rejected"/>
+    <x:cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="Pending"/>
+    <x:cfRule type="containsText" dxfId="20" priority="18" operator="containsText" text="Approved"/>
+    <x:cfRule type="containsText" dxfId="21" priority="19" operator="containsText" text="Corrected"/>
+    <x:cfRule type="containsText" dxfId="22" priority="20" operator="containsText" text="Rejected"/>
+    <x:cfRule type="containsText" dxfId="23" priority="21" operator="containsText" text="Pending"/>
+    <x:cfRule type="containsText" dxfId="24" priority="22" operator="containsText" text="Approved"/>
+    <x:cfRule type="containsText" dxfId="25" priority="23" operator="containsText" text="Corrected"/>
+    <x:cfRule type="containsText" dxfId="26" priority="24" operator="containsText" text="Rejected"/>
+    <x:cfRule type="containsText" dxfId="27" priority="25" operator="containsText" text="Pending"/>
+    <x:cfRule type="containsText" dxfId="28" priority="26" operator="containsText" text="Approved"/>
+    <x:cfRule type="containsText" dxfId="29" priority="27" operator="containsText" text="Corrected"/>
+    <x:cfRule type="containsText" dxfId="30" priority="28" operator="containsText" text="Rejected"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="E8:E37">
+      <x:formula1>"Pending,Approved,Corrected,Rejected"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="2">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73e87a68a24c4d20"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbef768b30a0e4826"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="45" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="40" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="40" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="58" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="34" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="15" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="42" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="16" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>Review Queue</x:v>
-      </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
-      <x:c r="G1" s="4"/>
-      <x:c r="H1" s="4"/>
-      <x:c r="I1" s="4"/>
-      <x:c r="J1" s="4"/>
-      <x:c r="K1" s="4"/>
-      <x:c r="L1" s="4"/>
-      <x:c r="M1" s="4"/>
-      <x:c r="N1" s="4"/>
-      <x:c r="O1" s="4"/>
-      <x:c r="P1" s="4"/>
-      <x:c r="Q1" s="4"/>
-      <x:c r="R1" s="4"/>
-      <x:c r="S1" s="4"/>
-    </x:row>
-    <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="8" t="str">
-        <x:v>One row per candidate. Editable cells are Status, human_relevant_chunk_ids, reviewer, reviewed_at, and correction_notes.</x:v>
-      </x:c>
-      <x:c r="B2" s="8"/>
-      <x:c r="C2" s="8"/>
-      <x:c r="D2" s="8"/>
-      <x:c r="E2" s="8"/>
-      <x:c r="F2" s="8"/>
-      <x:c r="G2" s="8"/>
-      <x:c r="H2" s="8"/>
-      <x:c r="I2" s="8"/>
-      <x:c r="J2" s="8"/>
-      <x:c r="K2" s="8"/>
-      <x:c r="L2" s="8"/>
-      <x:c r="M2" s="8"/>
-      <x:c r="N2" s="8"/>
-      <x:c r="O2" s="8"/>
-      <x:c r="P2" s="8"/>
-      <x:c r="Q2" s="8"/>
-      <x:c r="R2" s="8"/>
-      <x:c r="S2" s="8"/>
-    </x:row>
-    <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="28" t="str">
-        <x:v>question_id</x:v>
-      </x:c>
-      <x:c r="B5" s="58" t="str">
-        <x:v>seed_id</x:v>
-      </x:c>
-      <x:c r="C5" s="58" t="str">
-        <x:v>language</x:v>
-      </x:c>
-      <x:c r="D5" s="58" t="str">
-        <x:v>topic</x:v>
-      </x:c>
-      <x:c r="E5" s="58" t="str">
-        <x:v>difficulty</x:v>
-      </x:c>
-      <x:c r="F5" s="58" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="G5" s="58" t="str">
-        <x:v>expected_route</x:v>
-      </x:c>
-      <x:c r="H5" s="58" t="str">
-        <x:v>question</x:v>
-      </x:c>
-      <x:c r="I5" s="58" t="str">
-        <x:v>parent context</x:v>
-      </x:c>
-      <x:c r="J5" s="58" t="str">
-        <x:v>expected no result</x:v>
-      </x:c>
-      <x:c r="K5" s="58" t="str">
-        <x:v>proposed source IDs</x:v>
-      </x:c>
-      <x:c r="L5" s="58" t="str">
-        <x:v>proposed chunk IDs</x:v>
-      </x:c>
-      <x:c r="M5" s="58" t="str">
-        <x:v>proposed rationale</x:v>
-      </x:c>
-      <x:c r="N5" s="58" t="str">
-        <x:v>human_relevant_chunk_ids</x:v>
-      </x:c>
-      <x:c r="O5" s="58" t="str">
-        <x:v>reviewer</x:v>
-      </x:c>
-      <x:c r="P5" s="58" t="str">
-        <x:v>reviewed_at</x:v>
-      </x:c>
-      <x:c r="Q5" s="58" t="str">
-        <x:v>correction_notes</x:v>
-      </x:c>
-      <x:c r="R5" s="58" t="str">
-        <x:v>production mode</x:v>
-      </x:c>
-      <x:c r="S5" s="29" t="str">
-        <x:v>packet state</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="56" customHeight="1">
-      <x:c r="A6" s="64" t="str">
-        <x:v>gold30-001</x:v>
-      </x:c>
-      <x:c r="B6" s="64" t="str">
-        <x:v>expanded-111</x:v>
-      </x:c>
-      <x:c r="C6" s="64" t="str">
-        <x:v>English</x:v>
-      </x:c>
-      <x:c r="D6" s="64" t="str">
-        <x:v>current_measurements</x:v>
-      </x:c>
-      <x:c r="E6" s="64" t="str">
-        <x:v>easy</x:v>
-      </x:c>
-      <x:c r="F6" s="76" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G6" s="64" t="str">
-        <x:v>latest_measurements</x:v>
-      </x:c>
-      <x:c r="H6" s="64" t="str">
-        <x:v>What is the latest PM2.5 reading for Jakarta Pusat, and when was it observed?</x:v>
-      </x:c>
-      <x:c r="I6" s="64" t="str"/>
-      <x:c r="J6" s="64" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K6" s="64" t="str">
-        <x:v>jakarta-monitoring</x:v>
-      </x:c>
-      <x:c r="L6" s="64" t="str">
-        <x:v>jakarta-monitoring:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M6" s="64" t="str">
-        <x:v>The official station portal establishes that readings need a station, pollutant, value and timestamp; a current value must come from the measurement tool.</x:v>
-      </x:c>
-      <x:c r="N6" s="81" t="str"/>
-      <x:c r="O6" s="81" t="str"/>
-      <x:c r="P6" s="83"/>
-      <x:c r="Q6" s="81" t="str"/>
-      <x:c r="R6" s="64" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S6" s="64" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="56" customHeight="1">
-      <x:c r="A7" s="65" t="str">
-        <x:v>gold30-002</x:v>
-      </x:c>
-      <x:c r="B7" s="65" t="str">
-        <x:v>expanded-011</x:v>
-      </x:c>
-      <x:c r="C7" s="65" t="str">
-        <x:v>Bahasa Indonesia</x:v>
-      </x:c>
-      <x:c r="D7" s="65" t="str">
-        <x:v>current_measurements</x:v>
-      </x:c>
-      <x:c r="E7" s="65" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="F7" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G7" s="65" t="str">
-        <x:v>latest_measurements</x:v>
-      </x:c>
-      <x:c r="H7" s="65" t="str">
-        <x:v>Stasiun mana di Jakarta yang punya pembacaan ISPU terbaru paling tinggi?</x:v>
-      </x:c>
-      <x:c r="I7" s="65" t="str"/>
-      <x:c r="J7" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K7" s="65" t="str">
-        <x:v>jakarta-monitoring, ispu</x:v>
-      </x:c>
-      <x:c r="L7" s="65" t="str">
-        <x:v>jakarta-monitoring:structure:0 (p.1); ispu:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M7" s="65" t="str">
-        <x:v>Requires a current-station lookup plus the ISPU category interpretation; the corpus alone cannot substitute for a live observation.</x:v>
-      </x:c>
-      <x:c r="N7" s="82" t="str"/>
-      <x:c r="O7" s="82" t="str"/>
-      <x:c r="P7" s="84"/>
-      <x:c r="Q7" s="82" t="str"/>
-      <x:c r="R7" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S7" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="56" customHeight="1">
-      <x:c r="A8" s="65" t="str">
-        <x:v>gold30-003</x:v>
-      </x:c>
-      <x:c r="B8" s="65" t="str">
-        <x:v>expanded-001</x:v>
-      </x:c>
-      <x:c r="C8" s="65" t="str">
-        <x:v>English</x:v>
-      </x:c>
-      <x:c r="D8" s="65" t="str">
-        <x:v>current_measurements</x:v>
-      </x:c>
-      <x:c r="E8" s="65" t="str">
-        <x:v>easy</x:v>
-      </x:c>
-      <x:c r="F8" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G8" s="65" t="str">
-        <x:v>index_interpretation</x:v>
-      </x:c>
-      <x:c r="H8" s="65" t="str">
-        <x:v>Is an ISPU of 125 a concentration of 125 µg/m³?</x:v>
-      </x:c>
-      <x:c r="I8" s="65" t="str"/>
-      <x:c r="J8" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K8" s="65" t="str">
-        <x:v>ispu</x:v>
-      </x:c>
-      <x:c r="L8" s="65" t="str">
-        <x:v>ispu:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M8" s="65" t="str">
-        <x:v>The ISPU source explicitly separates the unitless index from a physical pollutant concentration.</x:v>
-      </x:c>
-      <x:c r="N8" s="82" t="str"/>
-      <x:c r="O8" s="82" t="str"/>
-      <x:c r="P8" s="84"/>
-      <x:c r="Q8" s="82" t="str"/>
-      <x:c r="R8" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S8" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="56" customHeight="1">
-      <x:c r="A9" s="65" t="str">
-        <x:v>gold30-004</x:v>
-      </x:c>
-      <x:c r="B9" s="65" t="str">
-        <x:v>expanded-016</x:v>
-      </x:c>
-      <x:c r="C9" s="65" t="str">
-        <x:v>Bahasa Indonesia</x:v>
-      </x:c>
-      <x:c r="D9" s="65" t="str">
-        <x:v>current_measurements</x:v>
-      </x:c>
-      <x:c r="E9" s="65" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="F9" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G9" s="65" t="str">
-        <x:v>latest_measurements</x:v>
-      </x:c>
-      <x:c r="H9" s="65" t="str">
-        <x:v>Tolong cek kualitas udara di Kepulauan Seribu—jika tidak ada data, apa yang bisa disimpulkan?</x:v>
-      </x:c>
-      <x:c r="I9" s="65" t="str"/>
-      <x:c r="J9" s="65" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="K9" s="65" t="str">
-        <x:v>jakarta-monitoring</x:v>
-      </x:c>
-      <x:c r="L9" s="65" t="str">
-        <x:v>jakarta-monitoring:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M9" s="65" t="str">
-        <x:v>This is a negative/no-result case: the answer should report absence of a matching observation rather than inventing a value; the portal source documents station scope.</x:v>
-      </x:c>
-      <x:c r="N9" s="82" t="str"/>
-      <x:c r="O9" s="82" t="str"/>
-      <x:c r="P9" s="84"/>
-      <x:c r="Q9" s="82" t="str"/>
-      <x:c r="R9" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S9" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="56" customHeight="1">
-      <x:c r="A10" s="65" t="str">
-        <x:v>gold30-005</x:v>
-      </x:c>
-      <x:c r="B10" s="65" t="str">
-        <x:v>expanded-006</x:v>
-      </x:c>
-      <x:c r="C10" s="65" t="str">
-        <x:v>English</x:v>
-      </x:c>
-      <x:c r="D10" s="65" t="str">
-        <x:v>historical_category_threshold</x:v>
-      </x:c>
-      <x:c r="E10" s="65" t="str">
-        <x:v>easy</x:v>
-      </x:c>
-      <x:c r="F10" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G10" s="65" t="str">
-        <x:v>index_interpretation</x:v>
-      </x:c>
-      <x:c r="H10" s="65" t="str">
-        <x:v>What does ISPU 45 mean, and how is that different from PM2.5 at 15 µg/m³?</x:v>
-      </x:c>
-      <x:c r="I10" s="65" t="str"/>
-      <x:c r="J10" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K10" s="65" t="str">
-        <x:v>ispu</x:v>
-      </x:c>
-      <x:c r="L10" s="65" t="str">
-        <x:v>ispu:structure:1 (p.2)</x:v>
-      </x:c>
-      <x:c r="M10" s="65" t="str">
-        <x:v>ISPU 45 is a category value, while PM2.5 is a concentration with units; the index source supports the distinction.</x:v>
-      </x:c>
-      <x:c r="N10" s="82" t="str"/>
-      <x:c r="O10" s="82" t="str"/>
-      <x:c r="P10" s="84"/>
-      <x:c r="Q10" s="82" t="str"/>
-      <x:c r="R10" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S10" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="56" customHeight="1">
-      <x:c r="A11" s="65" t="str">
-        <x:v>gold30-006</x:v>
-      </x:c>
-      <x:c r="B11" s="65" t="str">
-        <x:v>expanded-026</x:v>
-      </x:c>
-      <x:c r="C11" s="65" t="str">
-        <x:v>Bahasa Indonesia</x:v>
-      </x:c>
-      <x:c r="D11" s="65" t="str">
-        <x:v>historical_category_threshold</x:v>
-      </x:c>
-      <x:c r="E11" s="65" t="str">
-        <x:v>hard</x:v>
-      </x:c>
-      <x:c r="F11" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G11" s="65" t="str">
-        <x:v>guideline_vs_law</x:v>
-      </x:c>
-      <x:c r="H11" s="65" t="str">
-        <x:v>Berapa pedoman WHO PM2.5 tahunan dan 24 jam, dan apakah itu ambang hukum Indonesia?</x:v>
-      </x:c>
-      <x:c r="I11" s="65" t="str"/>
-      <x:c r="J11" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K11" s="65" t="str">
-        <x:v>who-aqg-2021-extract, jakarta-regulations</x:v>
-      </x:c>
-      <x:c r="L11" s="65" t="str">
-        <x:v>who-aqg-2021-extract:structure:2 (p.3); jakarta-regulations:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M11" s="65" t="str">
-        <x:v>Needs complementary WHO numeric guidance and Indonesian legal-status context; neither source alone answers both parts.</x:v>
-      </x:c>
-      <x:c r="N11" s="82" t="str"/>
-      <x:c r="O11" s="82" t="str"/>
-      <x:c r="P11" s="84"/>
-      <x:c r="Q11" s="82" t="str"/>
-      <x:c r="R11" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S11" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="56" customHeight="1">
-      <x:c r="A12" s="65" t="str">
-        <x:v>gold30-007</x:v>
-      </x:c>
-      <x:c r="B12" s="65" t="str">
-        <x:v>expanded-121</x:v>
-      </x:c>
-      <x:c r="C12" s="65" t="str">
-        <x:v>English</x:v>
-      </x:c>
-      <x:c r="D12" s="65" t="str">
-        <x:v>historical_category_threshold</x:v>
-      </x:c>
-      <x:c r="E12" s="65" t="str">
-        <x:v>easy</x:v>
-      </x:c>
-      <x:c r="F12" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G12" s="65" t="str">
-        <x:v>historical_provenance</x:v>
-      </x:c>
-      <x:c r="H12" s="65" t="str">
-        <x:v>Did Jakarta's historical PM2.5 series come from station sensors or a model?</x:v>
-      </x:c>
-      <x:c r="I12" s="65" t="str"/>
-      <x:c r="J12" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K12" s="65" t="str">
-        <x:v>jakarta-historical-city-series</x:v>
-      </x:c>
-      <x:c r="L12" s="65" t="str">
-        <x:v>jakarta-historical-city-series:structure:2 (p.3)</x:v>
-      </x:c>
-      <x:c r="M12" s="65" t="str">
-        <x:v>The historical-series provenance notes CAMS/Open-Meteo model concentrations rather than DKI station measurements.</x:v>
-      </x:c>
-      <x:c r="N12" s="82" t="str"/>
-      <x:c r="O12" s="82" t="str"/>
-      <x:c r="P12" s="84"/>
-      <x:c r="Q12" s="82" t="str"/>
-      <x:c r="R12" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S12" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="56" customHeight="1">
-      <x:c r="A13" s="65" t="str">
-        <x:v>gold30-008</x:v>
-      </x:c>
-      <x:c r="B13" s="65" t="str">
-        <x:v>expanded-126</x:v>
-      </x:c>
-      <x:c r="C13" s="65" t="str">
-        <x:v>Bahasa Indonesia</x:v>
-      </x:c>
-      <x:c r="D13" s="65" t="str">
-        <x:v>historical_category_threshold</x:v>
-      </x:c>
-      <x:c r="E13" s="65" t="str">
-        <x:v>easy</x:v>
-      </x:c>
-      <x:c r="F13" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G13" s="65" t="str">
-        <x:v>historical_provenance</x:v>
-      </x:c>
-      <x:c r="H13" s="65" t="str">
-        <x:v>Mengapa PM10 dan PM2.5 pada data historis dipisahkan?</x:v>
-      </x:c>
-      <x:c r="I13" s="65" t="str"/>
-      <x:c r="J13" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K13" s="65" t="str">
-        <x:v>jakarta-historical-city-series</x:v>
-      </x:c>
-      <x:c r="L13" s="65" t="str">
-        <x:v>jakarta-historical-city-series:structure:2 (p.3)</x:v>
-      </x:c>
-      <x:c r="M13" s="65" t="str">
-        <x:v>The series description defines PM10 and PM2.5 as separate pollutant variables with separate units and averaging.</x:v>
-      </x:c>
-      <x:c r="N13" s="82" t="str"/>
-      <x:c r="O13" s="82" t="str"/>
-      <x:c r="P13" s="84"/>
-      <x:c r="Q13" s="82" t="str"/>
-      <x:c r="R13" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S13" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="56" customHeight="1">
-      <x:c r="A14" s="65" t="str">
-        <x:v>gold30-009</x:v>
-      </x:c>
-      <x:c r="B14" s="65" t="str">
-        <x:v>expanded-021</x:v>
-      </x:c>
-      <x:c r="C14" s="65" t="str">
-        <x:v>English</x:v>
-      </x:c>
-      <x:c r="D14" s="65" t="str">
-        <x:v>historical_category_threshold</x:v>
-      </x:c>
-      <x:c r="E14" s="65" t="str">
-        <x:v>hard</x:v>
-      </x:c>
-      <x:c r="F14" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G14" s="65" t="str">
-        <x:v>guideline_vs_index</x:v>
-      </x:c>
-      <x:c r="H14" s="65" t="str">
-        <x:v>Can an ISPU category alone tell me whether the WHO annual guideline was met?</x:v>
-      </x:c>
-      <x:c r="I14" s="65" t="str"/>
-      <x:c r="J14" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K14" s="65" t="str">
-        <x:v>ispu, who-aqg-2021-extract</x:v>
-      </x:c>
-      <x:c r="L14" s="65" t="str">
-        <x:v>ispu:structure:0 (p.1); who-aqg-2021-extract:structure:2 (p.3)</x:v>
-      </x:c>
-      <x:c r="M14" s="65" t="str">
-        <x:v>Requires keeping an index category, concentration, pollutant and averaging period distinct; complementary sources are needed.</x:v>
-      </x:c>
-      <x:c r="N14" s="82" t="str"/>
-      <x:c r="O14" s="82" t="str"/>
-      <x:c r="P14" s="84"/>
-      <x:c r="Q14" s="82" t="str"/>
-      <x:c r="R14" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S14" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="56" customHeight="1">
-      <x:c r="A15" s="65" t="str">
-        <x:v>gold30-010</x:v>
-      </x:c>
-      <x:c r="B15" s="65" t="str">
-        <x:v>expanded-036</x:v>
-      </x:c>
-      <x:c r="C15" s="65" t="str">
-        <x:v>Bahasa Indonesia</x:v>
-      </x:c>
-      <x:c r="D15" s="65" t="str">
-        <x:v>causes</x:v>
-      </x:c>
-      <x:c r="E15" s="65" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="F15" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G15" s="65" t="str">
-        <x:v>source_apportionment</x:v>
-      </x:c>
-      <x:c r="H15" s="65" t="str">
-        <x:v>Sumber apa yang terkait dengan PM2.5 Jakarta, dan mengapa satu sumber tidak boleh langsung disebut penyebab pembacaan satu stasiun?</x:v>
-      </x:c>
-      <x:c r="I15" s="65" t="str"/>
-      <x:c r="J15" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K15" s="65" t="str">
-        <x:v>jakarta-causes</x:v>
-      </x:c>
-      <x:c r="L15" s="65" t="str">
-        <x:v>jakarta-causes:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M15" s="65" t="str">
-        <x:v>The causes record distinguishes likely contributors and cautions against causal claims about a single timestamped station reading.</x:v>
-      </x:c>
-      <x:c r="N15" s="82" t="str"/>
-      <x:c r="O15" s="82" t="str"/>
-      <x:c r="P15" s="84"/>
-      <x:c r="Q15" s="82" t="str"/>
-      <x:c r="R15" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S15" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="56" customHeight="1">
-      <x:c r="A16" s="65" t="str">
-        <x:v>gold30-011</x:v>
-      </x:c>
-      <x:c r="B16" s="65" t="str">
-        <x:v>expanded-122</x:v>
-      </x:c>
-      <x:c r="C16" s="65" t="str">
-        <x:v>English</x:v>
-      </x:c>
-      <x:c r="D16" s="65" t="str">
-        <x:v>causes</x:v>
-      </x:c>
-      <x:c r="E16" s="65" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="F16" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G16" s="65" t="str">
-        <x:v>source_apportionment</x:v>
-      </x:c>
-      <x:c r="H16" s="65" t="str">
-        <x:v>What is the difference between an emissions inventory and source apportionment?</x:v>
-      </x:c>
-      <x:c r="I16" s="65" t="str"/>
-      <x:c r="J16" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K16" s="65" t="str">
-        <x:v>jakarta-causes</x:v>
-      </x:c>
-      <x:c r="L16" s="65" t="str">
-        <x:v>jakarta-causes:structure:1 (p.2)</x:v>
-      </x:c>
-      <x:c r="M16" s="65" t="str">
-        <x:v>The causes record explains the different methods and their interpretation limits.</x:v>
-      </x:c>
-      <x:c r="N16" s="82" t="str"/>
-      <x:c r="O16" s="82" t="str"/>
-      <x:c r="P16" s="84"/>
-      <x:c r="Q16" s="82" t="str"/>
-      <x:c r="R16" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S16" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="56" customHeight="1">
-      <x:c r="A17" s="65" t="str">
-        <x:v>gold30-012</x:v>
-      </x:c>
-      <x:c r="B17" s="65" t="str">
-        <x:v>expanded-041</x:v>
-      </x:c>
-      <x:c r="C17" s="65" t="str">
-        <x:v>Bahasa Indonesia</x:v>
-      </x:c>
-      <x:c r="D17" s="65" t="str">
-        <x:v>causes</x:v>
-      </x:c>
-      <x:c r="E17" s="65" t="str">
-        <x:v>hard</x:v>
-      </x:c>
-      <x:c r="F17" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G17" s="65" t="str">
-        <x:v>causal_inference</x:v>
-      </x:c>
-      <x:c r="H17" s="65" t="str">
-        <x:v>Apakah pembacaan tinggi di jalan saya membuktikan pabrik menjadi penyebabnya?</x:v>
-      </x:c>
-      <x:c r="I17" s="65" t="str"/>
-      <x:c r="J17" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K17" s="65" t="str">
-        <x:v>jakarta-causes</x:v>
-      </x:c>
-      <x:c r="L17" s="65" t="str">
-        <x:v>jakarta-causes:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M17" s="65" t="str">
-        <x:v>Ambiguous causal question; the source supports multiple contributors and explicitly rejects assigning one cause to one reading without local evidence.</x:v>
-      </x:c>
-      <x:c r="N17" s="82" t="str"/>
-      <x:c r="O17" s="82" t="str"/>
-      <x:c r="P17" s="84"/>
-      <x:c r="Q17" s="82" t="str"/>
-      <x:c r="R17" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S17" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="56" customHeight="1">
-      <x:c r="A18" s="65" t="str">
-        <x:v>gold30-013</x:v>
-      </x:c>
-      <x:c r="B18" s="65" t="str">
-        <x:v>expanded-031</x:v>
-      </x:c>
-      <x:c r="C18" s="65" t="str">
-        <x:v>English</x:v>
-      </x:c>
-      <x:c r="D18" s="65" t="str">
-        <x:v>causes</x:v>
-      </x:c>
-      <x:c r="E18" s="65" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="F18" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G18" s="65" t="str">
-        <x:v>regional_sources</x:v>
-      </x:c>
-      <x:c r="H18" s="65" t="str">
-        <x:v>Does Jakarta's air pollution come only from inside the city?</x:v>
-      </x:c>
-      <x:c r="I18" s="65" t="str"/>
-      <x:c r="J18" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K18" s="65" t="str">
-        <x:v>jakarta-causes, jakarta-policy-implementation</x:v>
-      </x:c>
-      <x:c r="L18" s="65" t="str">
-        <x:v>jakarta-causes:structure:0 (p.1); jakarta-policy-implementation:structure:2 (p.3)</x:v>
-      </x:c>
-      <x:c r="M18" s="65" t="str">
-        <x:v>Needs the causes discussion of local and regional sources and the implementation record's airshed/coordination context.</x:v>
-      </x:c>
-      <x:c r="N18" s="82" t="str"/>
-      <x:c r="O18" s="82" t="str"/>
-      <x:c r="P18" s="84"/>
-      <x:c r="Q18" s="82" t="str"/>
-      <x:c r="R18" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S18" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="56" customHeight="1">
-      <x:c r="A19" s="65" t="str">
-        <x:v>gold30-014</x:v>
-      </x:c>
-      <x:c r="B19" s="65" t="str">
-        <x:v>expanded-051</x:v>
-      </x:c>
-      <x:c r="C19" s="65" t="str">
-        <x:v>Bahasa Indonesia</x:v>
-      </x:c>
-      <x:c r="D19" s="65" t="str">
-        <x:v>regulations_implementation</x:v>
-      </x:c>
-      <x:c r="E19" s="65" t="str">
-        <x:v>hard</x:v>
-      </x:c>
-      <x:c r="F19" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G19" s="65" t="str">
-        <x:v>regulation_current</x:v>
-      </x:c>
-      <x:c r="H19" s="65" t="str">
-        <x:v>Apakah Pergub 66/2020 masih tercatat berlaku, dan apa yang dibuktikannya tentang penegakan?</x:v>
-      </x:c>
-      <x:c r="I19" s="65" t="str"/>
-      <x:c r="J19" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K19" s="65" t="str">
-        <x:v>pergub-66-2020-vehicle-testing, jakarta-emission-testing</x:v>
-      </x:c>
-      <x:c r="L19" s="65" t="str">
-        <x:v>pergub-66-2020-vehicle-testing:structure:0 (p.1); jakarta-emission-testing:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M19" s="65" t="str">
-        <x:v>Separates legal status from evidence of enforcement; the legal record and DKI FAQ provide complementary context.</x:v>
-      </x:c>
-      <x:c r="N19" s="82" t="str"/>
-      <x:c r="O19" s="82" t="str"/>
-      <x:c r="P19" s="84"/>
-      <x:c r="Q19" s="82" t="str"/>
-      <x:c r="R19" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S19" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="56" customHeight="1">
-      <x:c r="A20" s="65" t="str">
-        <x:v>gold30-015</x:v>
-      </x:c>
-      <x:c r="B20" s="65" t="str">
-        <x:v>expanded-056</x:v>
-      </x:c>
-      <x:c r="C20" s="65" t="str">
-        <x:v>English</x:v>
-      </x:c>
-      <x:c r="D20" s="65" t="str">
-        <x:v>regulations_implementation</x:v>
-      </x:c>
-      <x:c r="E20" s="65" t="str">
-        <x:v>easy</x:v>
-      </x:c>
-      <x:c r="F20" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G20" s="65" t="str">
-        <x:v>regulation_scope</x:v>
-      </x:c>
-      <x:c r="H20" s="65" t="str">
-        <x:v>Which vehicle categories and ages are covered by Permen LHK 8/2023?</x:v>
-      </x:c>
-      <x:c r="I20" s="65" t="str"/>
-      <x:c r="J20" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K20" s="65" t="str">
-        <x:v>permen-lhk-8-2023-vehicle-emissions</x:v>
-      </x:c>
-      <x:c r="L20" s="65" t="str">
-        <x:v>permen-lhk-8-2023-vehicle-emissions:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M20" s="65" t="str">
-        <x:v>The official abstract states categories M, N, O and L and the more-than-three-years condition.</x:v>
-      </x:c>
-      <x:c r="N20" s="82" t="str"/>
-      <x:c r="O20" s="82" t="str"/>
-      <x:c r="P20" s="84"/>
-      <x:c r="Q20" s="82" t="str"/>
-      <x:c r="R20" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S20" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="56" customHeight="1">
-      <x:c r="A21" s="65" t="str">
-        <x:v>gold30-016</x:v>
-      </x:c>
-      <x:c r="B21" s="65" t="str">
-        <x:v>expanded-061</x:v>
-      </x:c>
-      <x:c r="C21" s="65" t="str">
-        <x:v>Bahasa Indonesia</x:v>
-      </x:c>
-      <x:c r="D21" s="65" t="str">
-        <x:v>regulations_implementation</x:v>
-      </x:c>
-      <x:c r="E21" s="65" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="F21" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G21" s="65" t="str">
-        <x:v>implementation_evidence</x:v>
-      </x:c>
-      <x:c r="H21" s="65" t="str">
-        <x:v>Apakah konektivitas CEMS menunjukkan bahwa setiap cerobong sudah memenuhi batas emisi?</x:v>
-      </x:c>
-      <x:c r="I21" s="65" t="str"/>
-      <x:c r="J21" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K21" s="65" t="str">
-        <x:v>permen-lhk-13-2021-cems, jakarta-cems-monitoring</x:v>
-      </x:c>
-      <x:c r="L21" s="65" t="str">
-        <x:v>permen-lhk-13-2021-cems:structure:0 (p.1); jakarta-cems-monitoring:structure:1 (p.2)</x:v>
-      </x:c>
-      <x:c r="M21" s="65" t="str">
-        <x:v>Requires the regulation's CEMS boundary and the DKI monitoring-programme caveat that connectivity is not compliance proof.</x:v>
-      </x:c>
-      <x:c r="N21" s="82" t="str"/>
-      <x:c r="O21" s="82" t="str"/>
-      <x:c r="P21" s="84"/>
-      <x:c r="Q21" s="82" t="str"/>
-      <x:c r="R21" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S21" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="56" customHeight="1">
-      <x:c r="A22" s="65" t="str">
-        <x:v>gold30-017</x:v>
-      </x:c>
-      <x:c r="B22" s="65" t="str">
-        <x:v>expanded-066</x:v>
-      </x:c>
-      <x:c r="C22" s="65" t="str">
-        <x:v>English</x:v>
-      </x:c>
-      <x:c r="D22" s="65" t="str">
-        <x:v>regulations_implementation</x:v>
-      </x:c>
-      <x:c r="E22" s="65" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="F22" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G22" s="65" t="str">
-        <x:v>court_record_status</x:v>
-      </x:c>
-      <x:c r="H22" s="65" t="str">
-        <x:v>What does the Jakarta air-pollution court record establish, and does it prove every order was implemented?</x:v>
-      </x:c>
-      <x:c r="I22" s="65" t="str"/>
-      <x:c r="J22" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K22" s="65" t="str">
-        <x:v>jakarta-court-air-quality, ma-jakarta-air-lawsuit-record</x:v>
-      </x:c>
-      <x:c r="L22" s="65" t="str">
-        <x:v>jakarta-court-air-quality:structure:1 (p.2); ma-jakarta-air-lawsuit-record:structure:1 (p.2)</x:v>
-      </x:c>
-      <x:c r="M22" s="65" t="str">
-        <x:v>Court-record identity and execution status are separate questions; both normalized records state that implementation needs later verification.</x:v>
-      </x:c>
-      <x:c r="N22" s="82" t="str"/>
-      <x:c r="O22" s="82" t="str"/>
-      <x:c r="P22" s="84"/>
-      <x:c r="Q22" s="82" t="str"/>
-      <x:c r="R22" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S22" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="56" customHeight="1">
-      <x:c r="A23" s="65" t="str">
-        <x:v>gold30-018</x:v>
-      </x:c>
-      <x:c r="B23" s="65" t="str">
-        <x:v>expanded-062</x:v>
-      </x:c>
-      <x:c r="C23" s="65" t="str">
-        <x:v>Bahasa Indonesia</x:v>
-      </x:c>
-      <x:c r="D23" s="65" t="str">
-        <x:v>regulations_implementation</x:v>
-      </x:c>
-      <x:c r="E23" s="65" t="str">
-        <x:v>hard</x:v>
-      </x:c>
-      <x:c r="F23" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G23" s="65" t="str">
-        <x:v>policy_implementation</x:v>
-      </x:c>
-      <x:c r="H23" s="65" t="str">
-        <x:v>Mengapa aturan dapat tetap ada sementara kualitas udara Jakarta masih buruk?</x:v>
-      </x:c>
-      <x:c r="I23" s="65" t="str"/>
-      <x:c r="J23" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K23" s="65" t="str">
-        <x:v>jakarta-policy-implementation, jakarta-regulations, jakarta-court-air-quality</x:v>
-      </x:c>
-      <x:c r="L23" s="65" t="str">
-        <x:v>jakarta-policy-implementation:structure:0 (p.1); jakarta-regulations:structure:0 (p.1); jakarta-court-air-quality:structure:1 (p.2)</x:v>
-      </x:c>
-      <x:c r="M23" s="65" t="str">
-        <x:v>Complementary rule-on-paper, implementation-gap and court context are required for a cautious explanation.</x:v>
-      </x:c>
-      <x:c r="N23" s="82" t="str"/>
-      <x:c r="O23" s="82" t="str"/>
-      <x:c r="P23" s="84"/>
-      <x:c r="Q23" s="82" t="str"/>
-      <x:c r="R23" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S23" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="56" customHeight="1">
-      <x:c r="A24" s="65" t="str">
-        <x:v>gold30-019</x:v>
-      </x:c>
-      <x:c r="B24" s="65" t="str">
-        <x:v>expanded-091</x:v>
-      </x:c>
-      <x:c r="C24" s="65" t="str">
-        <x:v>English</x:v>
-      </x:c>
-      <x:c r="D24" s="65" t="str">
-        <x:v>protection_individual_action</x:v>
-      </x:c>
-      <x:c r="E24" s="65" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="F24" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G24" s="65" t="str">
-        <x:v>exposure_reduction</x:v>
-      </x:c>
-      <x:c r="H24" s="65" t="str">
-        <x:v>What should I do on a bad-air day, and do masks replace clean-air policy?</x:v>
-      </x:c>
-      <x:c r="I24" s="65" t="str"/>
-      <x:c r="J24" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K24" s="65" t="str">
-        <x:v>bad-air-day-protection, exposure-protection</x:v>
-      </x:c>
-      <x:c r="L24" s="65" t="str">
-        <x:v>bad-air-day-protection:structure:3 (p.4); exposure-protection:structure:1 (p.2)</x:v>
-      </x:c>
-      <x:c r="M24" s="65" t="str">
-        <x:v>The health guidance covers immediate exposure reduction and the explicit limit that personal protection cannot replace emissions policy.</x:v>
-      </x:c>
-      <x:c r="N24" s="82" t="str"/>
-      <x:c r="O24" s="82" t="str"/>
-      <x:c r="P24" s="84"/>
-      <x:c r="Q24" s="82" t="str"/>
-      <x:c r="R24" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S24" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="56" customHeight="1">
-      <x:c r="A25" s="65" t="str">
-        <x:v>gold30-020</x:v>
-      </x:c>
-      <x:c r="B25" s="65" t="str">
-        <x:v>expanded-096</x:v>
-      </x:c>
-      <x:c r="C25" s="65" t="str">
-        <x:v>Bahasa Indonesia</x:v>
-      </x:c>
-      <x:c r="D25" s="65" t="str">
-        <x:v>protection_individual_action</x:v>
-      </x:c>
-      <x:c r="E25" s="65" t="str">
-        <x:v>easy</x:v>
-      </x:c>
-      <x:c r="F25" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G25" s="65" t="str">
-        <x:v>indoor_filtration</x:v>
-      </x:c>
-      <x:c r="H25" s="65" t="str">
-        <x:v>Bagaimana memilih pembersih udara untuk kamar 20 m², dan apa batasannya?</x:v>
-      </x:c>
-      <x:c r="I25" s="65" t="str"/>
-      <x:c r="J25" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K25" s="65" t="str">
-        <x:v>clean-air-room</x:v>
-      </x:c>
-      <x:c r="L25" s="65" t="str">
-        <x:v>clean-air-room:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M25" s="65" t="str">
-        <x:v>The EPA-derived room-sizing and limitation guidance supports a cautious engineering answer, not a local health guarantee.</x:v>
-      </x:c>
-      <x:c r="N25" s="82" t="str"/>
-      <x:c r="O25" s="82" t="str"/>
-      <x:c r="P25" s="84"/>
-      <x:c r="Q25" s="82" t="str"/>
-      <x:c r="R25" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S25" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="56" customHeight="1">
-      <x:c r="A26" s="65" t="str">
-        <x:v>gold30-021</x:v>
-      </x:c>
-      <x:c r="B26" s="65" t="str">
-        <x:v>expanded-101</x:v>
-      </x:c>
-      <x:c r="C26" s="65" t="str">
-        <x:v>English</x:v>
-      </x:c>
-      <x:c r="D26" s="65" t="str">
-        <x:v>protection_individual_action</x:v>
-      </x:c>
-      <x:c r="E26" s="65" t="str">
-        <x:v>easy</x:v>
-      </x:c>
-      <x:c r="F26" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G26" s="65" t="str">
-        <x:v>respirator_limits</x:v>
-      </x:c>
-      <x:c r="H26" s="65" t="str">
-        <x:v>Is an N95-style particulate respirator protection against every pollutant?</x:v>
-      </x:c>
-      <x:c r="I26" s="65" t="str"/>
-      <x:c r="J26" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K26" s="65" t="str">
-        <x:v>who-personal-interventions-2024, exposure-protection</x:v>
-      </x:c>
-      <x:c r="L26" s="65" t="str">
-        <x:v>who-personal-interventions-2024:structure:3 (p.4); exposure-protection:structure:1 (p.2)</x:v>
-      </x:c>
-      <x:c r="M26" s="65" t="str">
-        <x:v>The guidance supports particulate protection with fit caveats and says respirators do not filter every gas.</x:v>
-      </x:c>
-      <x:c r="N26" s="82" t="str"/>
-      <x:c r="O26" s="82" t="str"/>
-      <x:c r="P26" s="84"/>
-      <x:c r="Q26" s="82" t="str"/>
-      <x:c r="R26" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S26" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="56" customHeight="1">
-      <x:c r="A27" s="65" t="str">
-        <x:v>gold30-022</x:v>
-      </x:c>
-      <x:c r="B27" s="65" t="str">
-        <x:v>expanded-081</x:v>
-      </x:c>
-      <x:c r="C27" s="65" t="str">
-        <x:v>Bahasa Indonesia</x:v>
-      </x:c>
-      <x:c r="D27" s="65" t="str">
-        <x:v>protection_individual_action</x:v>
-      </x:c>
-      <x:c r="E27" s="65" t="str">
-        <x:v>easy</x:v>
-      </x:c>
-      <x:c r="F27" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G27" s="65" t="str">
-        <x:v>individual_emission_reduction</x:v>
-      </x:c>
-      <x:c r="H27" s="65" t="str">
-        <x:v>Apa yang bisa saya lakukan untuk mengurangi emisi dan melaporkan kendaraan berasap?</x:v>
-      </x:c>
-      <x:c r="I27" s="65" t="str"/>
-      <x:c r="J27" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K27" s="65" t="str">
-        <x:v>individual-emission-actions</x:v>
-      </x:c>
-      <x:c r="L27" s="65" t="str">
-        <x:v>individual-emission-actions:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M27" s="65" t="str">
-        <x:v>The civic-actions source covers lower-emission travel, vehicle maintenance and evidence-preserving reports.</x:v>
-      </x:c>
-      <x:c r="N27" s="82" t="str"/>
-      <x:c r="O27" s="82" t="str"/>
-      <x:c r="P27" s="84"/>
-      <x:c r="Q27" s="82" t="str"/>
-      <x:c r="R27" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S27" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="56" customHeight="1">
-      <x:c r="A28" s="65" t="str">
-        <x:v>gold30-023</x:v>
-      </x:c>
-      <x:c r="B28" s="65" t="str">
-        <x:v>expanded-142</x:v>
-      </x:c>
-      <x:c r="C28" s="65" t="str">
-        <x:v>English</x:v>
-      </x:c>
-      <x:c r="D28" s="65" t="str">
-        <x:v>protection_individual_action</x:v>
-      </x:c>
-      <x:c r="E28" s="65" t="str">
-        <x:v>hard</x:v>
-      </x:c>
-      <x:c r="F28" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G28" s="65" t="str">
-        <x:v>exposure_reduction</x:v>
-      </x:c>
-      <x:c r="H28" s="65" t="str">
-        <x:v>Does staying indoors always reduce exposure during a pollution episode?</x:v>
-      </x:c>
-      <x:c r="I28" s="65" t="str"/>
-      <x:c r="J28" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K28" s="65" t="str">
-        <x:v>exposure-protection, clean-air-room, bad-air-day-protection</x:v>
-      </x:c>
-      <x:c r="L28" s="65" t="str">
-        <x:v>exposure-protection:structure:0 (p.1); clean-air-room:structure:3 (p.4); bad-air-day-protection:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M28" s="65" t="str">
-        <x:v>Hard boundary case: indoors helps only when indoor air is cleaner and indoor sources, filtration, ventilation and infiltration are considered.</x:v>
-      </x:c>
-      <x:c r="N28" s="82" t="str"/>
-      <x:c r="O28" s="82" t="str"/>
-      <x:c r="P28" s="84"/>
-      <x:c r="Q28" s="82" t="str"/>
-      <x:c r="R28" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S28" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="56" customHeight="1">
-      <x:c r="A29" s="65" t="str">
-        <x:v>gold30-024</x:v>
-      </x:c>
-      <x:c r="B29" s="65" t="str">
-        <x:v>expanded-027</x:v>
-      </x:c>
-      <x:c r="C29" s="65" t="str">
-        <x:v>Bahasa Indonesia</x:v>
-      </x:c>
-      <x:c r="D29" s="65" t="str">
-        <x:v>multi_turn_followups</x:v>
-      </x:c>
-      <x:c r="E29" s="65" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="F29" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G29" s="65" t="str">
-        <x:v>guideline_vs_law</x:v>
-      </x:c>
-      <x:c r="H29" s="65" t="str">
-        <x:v>Apa perbedaan aturan kualitas udara Jakarta yang berlaku dengan pedoman WHO?</x:v>
-      </x:c>
-      <x:c r="I29" s="65" t="str">
-        <x:v>conv-024: Peraturan kualitas udara apa yang saat ini berlaku di Jakarta?</x:v>
-      </x:c>
-      <x:c r="J29" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K29" s="65" t="str">
-        <x:v>jakarta-regulations, who-aqg-2021-extract</x:v>
-      </x:c>
-      <x:c r="L29" s="65" t="str">
-        <x:v>jakarta-regulations:structure:0 (p.1); who-aqg-2021-extract:structure:1 (p.2)</x:v>
-      </x:c>
-      <x:c r="M29" s="65" t="str">
-        <x:v>Follow-up inherits the regulation context and asks for a law-versus-guideline distinction using complementary sources.</x:v>
-      </x:c>
-      <x:c r="N29" s="82" t="str"/>
-      <x:c r="O29" s="82" t="str"/>
-      <x:c r="P29" s="84"/>
-      <x:c r="Q29" s="82" t="str"/>
-      <x:c r="R29" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S29" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="56" customHeight="1">
-      <x:c r="A30" s="65" t="str">
-        <x:v>gold30-025</x:v>
-      </x:c>
-      <x:c r="B30" s="65" t="str">
-        <x:v>expanded-103</x:v>
-      </x:c>
-      <x:c r="C30" s="65" t="str">
-        <x:v>English</x:v>
-      </x:c>
-      <x:c r="D30" s="65" t="str">
-        <x:v>multi_turn_followups</x:v>
-      </x:c>
-      <x:c r="E30" s="65" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="F30" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G30" s="65" t="str">
-        <x:v>category_interpretation</x:v>
-      </x:c>
-      <x:c r="H30" s="65" t="str">
-        <x:v>Does Jakarta Utara being categorized as Good most recently mean the air was safe all day?</x:v>
-      </x:c>
-      <x:c r="I30" s="65" t="str">
-        <x:v>conv-025: When was Jakarta Utara most recently categorized as Good?</x:v>
-      </x:c>
-      <x:c r="J30" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K30" s="65" t="str">
-        <x:v>jakarta-monitoring, ispu, health-disclaimer</x:v>
-      </x:c>
-      <x:c r="L30" s="65" t="str">
-        <x:v>jakarta-monitoring:structure:0 (p.1); ispu:structure:0 (p.1); health-disclaimer:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M30" s="65" t="str">
-        <x:v>Follow-up must preserve timestamp/category limits and avoid converting one observation into an all-day or medical conclusion.</x:v>
-      </x:c>
-      <x:c r="N30" s="82" t="str"/>
-      <x:c r="O30" s="82" t="str"/>
-      <x:c r="P30" s="84"/>
-      <x:c r="Q30" s="82" t="str"/>
-      <x:c r="R30" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S30" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="56" customHeight="1">
-      <x:c r="A31" s="65" t="str">
-        <x:v>gold30-026</x:v>
-      </x:c>
-      <x:c r="B31" s="65" t="str">
-        <x:v>expanded-092</x:v>
-      </x:c>
-      <x:c r="C31" s="65" t="str">
-        <x:v>Bahasa Indonesia</x:v>
-      </x:c>
-      <x:c r="D31" s="65" t="str">
-        <x:v>multi_turn_followups</x:v>
-      </x:c>
-      <x:c r="E31" s="65" t="str">
-        <x:v>hard</x:v>
-      </x:c>
-      <x:c r="F31" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G31" s="65" t="str">
-        <x:v>measurement_vs_guideline</x:v>
-      </x:c>
-      <x:c r="H31" s="65" t="str">
-        <x:v>Bisakah Anda membandingkan PM2.5 Jakarta Pusat dengan pedoman WHO 24 jam sambil mempertahankan waktu pengamatan dan satuannya?</x:v>
-      </x:c>
-      <x:c r="I31" s="65" t="str">
-        <x:v>conv-026: Berapa kadar PM2.5 terbaru di Jakarta Pusat?</x:v>
-      </x:c>
-      <x:c r="J31" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K31" s="65" t="str">
-        <x:v>jakarta-monitoring, who-aqg-2021-extract</x:v>
-      </x:c>
-      <x:c r="L31" s="65" t="str">
-        <x:v>jakarta-monitoring:structure:0 (p.1); who-aqg-2021-extract:structure:2 (p.3)</x:v>
-      </x:c>
-      <x:c r="M31" s="65" t="str">
-        <x:v>Requires a current measurement tool result plus WHO's 24-hour value while preserving timestamp, pollutant and units.</x:v>
-      </x:c>
-      <x:c r="N31" s="82" t="str"/>
-      <x:c r="O31" s="82" t="str"/>
-      <x:c r="P31" s="84"/>
-      <x:c r="Q31" s="82" t="str"/>
-      <x:c r="R31" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S31" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="56" customHeight="1">
-      <x:c r="A32" s="65" t="str">
-        <x:v>gold30-027</x:v>
-      </x:c>
-      <x:c r="B32" s="65" t="str">
-        <x:v>expanded-042</x:v>
-      </x:c>
-      <x:c r="C32" s="65" t="str">
-        <x:v>English</x:v>
-      </x:c>
-      <x:c r="D32" s="65" t="str">
-        <x:v>multi_turn_followups</x:v>
-      </x:c>
-      <x:c r="E32" s="65" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="F32" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G32" s="65" t="str">
-        <x:v>causal_inference</x:v>
-      </x:c>
-      <x:c r="H32" s="65" t="str">
-        <x:v>So does that mean vehicles definitely caused my station's reading today?</x:v>
-      </x:c>
-      <x:c r="I32" s="65" t="str">
-        <x:v>conv-027: What are the main sources of Jakarta PM2.5?</x:v>
-      </x:c>
-      <x:c r="J32" s="65" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="K32" s="65" t="str">
-        <x:v>jakarta-causes, jakarta-monitoring</x:v>
-      </x:c>
-      <x:c r="L32" s="65" t="str">
-        <x:v>jakarta-causes:structure:2 (p.3); jakarta-monitoring:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M32" s="65" t="str">
-        <x:v>Follow-up tests whether likely contributors are incorrectly turned into proof of a single reading's cause.</x:v>
-      </x:c>
-      <x:c r="N32" s="82" t="str"/>
-      <x:c r="O32" s="82" t="str"/>
-      <x:c r="P32" s="84"/>
-      <x:c r="Q32" s="82" t="str"/>
-      <x:c r="R32" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S32" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="56" customHeight="1">
-      <x:c r="A33" s="65" t="str">
-        <x:v>gold30-028</x:v>
-      </x:c>
-      <x:c r="B33" s="65" t="str">
-        <x:v>expanded-143</x:v>
-      </x:c>
-      <x:c r="C33" s="65" t="str">
-        <x:v>Bahasa Indonesia</x:v>
-      </x:c>
-      <x:c r="D33" s="65" t="str">
-        <x:v>missing_data_safety_abstention</x:v>
-      </x:c>
-      <x:c r="E33" s="65" t="str">
-        <x:v>easy</x:v>
-      </x:c>
-      <x:c r="F33" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G33" s="65" t="str">
-        <x:v>health_abstention</x:v>
-      </x:c>
-      <x:c r="H33" s="65" t="str">
-        <x:v>Bisakah informasi ini mendiagnosis apakah sesak dada saya disebabkan polusi udara?</x:v>
-      </x:c>
-      <x:c r="I33" s="65" t="str"/>
-      <x:c r="J33" s="65" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="K33" s="65" t="str">
-        <x:v>health-disclaimer</x:v>
-      </x:c>
-      <x:c r="L33" s="65" t="str">
-        <x:v>health-disclaimer:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M33" s="65" t="str">
-        <x:v>The health boundary explicitly says air-quality information is educational and does not diagnose an individual; severe or persistent symptoms need care.</x:v>
-      </x:c>
-      <x:c r="N33" s="82" t="str"/>
-      <x:c r="O33" s="82" t="str"/>
-      <x:c r="P33" s="84"/>
-      <x:c r="Q33" s="82" t="str"/>
-      <x:c r="R33" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S33" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="56" customHeight="1">
-      <x:c r="A34" s="65" t="str">
-        <x:v>gold30-029</x:v>
-      </x:c>
-      <x:c r="B34" s="65" t="str">
-        <x:v>expanded-113</x:v>
-      </x:c>
-      <x:c r="C34" s="65" t="str">
-        <x:v>English</x:v>
-      </x:c>
-      <x:c r="D34" s="65" t="str">
-        <x:v>missing_data_safety_abstention</x:v>
-      </x:c>
-      <x:c r="E34" s="65" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="F34" s="77" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G34" s="65" t="str">
-        <x:v>missing_measurement_abstention</x:v>
-      </x:c>
-      <x:c r="H34" s="65" t="str">
-        <x:v>The station's PM2.5 value is blank; can you fill it with Jakarta's average?</x:v>
-      </x:c>
-      <x:c r="I34" s="65" t="str"/>
-      <x:c r="J34" s="65" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="K34" s="65" t="str">
-        <x:v>jakarta-monitoring</x:v>
-      </x:c>
-      <x:c r="L34" s="65" t="str">
-        <x:v>jakarta-monitoring:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M34" s="65" t="str">
-        <x:v>Negative-data case: a missing station value must not be replaced with an unrelated average; the portal provides provenance requirements.</x:v>
-      </x:c>
-      <x:c r="N34" s="82" t="str"/>
-      <x:c r="O34" s="82" t="str"/>
-      <x:c r="P34" s="84"/>
-      <x:c r="Q34" s="82" t="str"/>
-      <x:c r="R34" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S34" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="56" customHeight="1">
-      <x:c r="A35" s="65" t="str">
-        <x:v>gold30-030</x:v>
-      </x:c>
-      <x:c r="B35" s="65" t="str">
-        <x:v>expanded-131</x:v>
-      </x:c>
-      <x:c r="C35" s="65" t="str">
-        <x:v>Bahasa Indonesia</x:v>
-      </x:c>
-      <x:c r="D35" s="65" t="str">
-        <x:v>missing_data_safety_abstention</x:v>
-      </x:c>
-      <x:c r="E35" s="65" t="str">
-        <x:v>hard</x:v>
-      </x:c>
-      <x:c r="F35" s="78" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="G35" s="65" t="str">
-        <x:v>implementation_abstention</x:v>
-      </x:c>
-      <x:c r="H35" s="65" t="str">
-        <x:v>Ringkasan putusan tidak punya tanggal penyelesaian; bolehkah kita mengatakan perintahnya sudah dilaksanakan?</x:v>
-      </x:c>
-      <x:c r="I35" s="65" t="str"/>
-      <x:c r="J35" s="65" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="K35" s="65" t="str">
-        <x:v>ma-jakarta-air-lawsuit-record, jakarta-policy-implementation</x:v>
-      </x:c>
-      <x:c r="L35" s="65" t="str">
-        <x:v>ma-jakarta-air-lawsuit-record:structure:0 (p.1); jakarta-policy-implementation:structure:0 (p.1)</x:v>
-      </x:c>
-      <x:c r="M35" s="65" t="str">
-        <x:v>The court record explicitly withholds completion claims without subsequent execution evidence.</x:v>
-      </x:c>
-      <x:c r="N35" s="82" t="str"/>
-      <x:c r="O35" s="82" t="str"/>
-      <x:c r="P35" s="84"/>
-      <x:c r="Q35" s="82" t="str"/>
-      <x:c r="R35" s="65" t="str">
-        <x:v>hybrid_rerank</x:v>
-      </x:c>
-      <x:c r="S35" s="65" t="str">
-        <x:v>pending_human</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:S1"/>
-    <x:mergeCell ref="A2:S2"/>
-  </x:mergeCells>
-  <x:conditionalFormatting sqref="F6:F35">
-    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Approved"/>
-    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Corrected"/>
-    <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Rejected"/>
-  </x:conditionalFormatting>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="F6:F35">
-      <x:formula1>"Pending,Approved,Corrected,Rejected"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re994873f0e8c42cd"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -27430,12 +28662,12 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d1122c3611c4b4f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77e837e6baf4494d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
